--- a/2025逐项来源清单.xlsx
+++ b/2025逐项来源清单.xlsx
@@ -709,7 +709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P396"/>
+  <dimension ref="A1:Q396"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -728,6 +728,7 @@
     <col width="52" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="17" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -818,6 +819,11 @@
           <t>处理动作</t>
         </is>
       </c>
+      <c r="Q2" s="22" t="inlineStr">
+        <is>
+          <t>2025集团口径复核（2026-10外部回源）</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="43.59999999999999" customHeight="1">
       <c r="A3" s="23" t="n">
@@ -898,6 +904,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q3" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="56.8" customHeight="1">
       <c r="A4" s="23" t="n">
@@ -978,6 +989,11 @@
           <t>已修正（56.6%→50.61%）+已换源（官网→评级报告）</t>
         </is>
       </c>
+      <c r="Q4" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="30.4" customHeight="1">
       <c r="A5" s="23" t="n">
@@ -1058,6 +1074,11 @@
           <t>已修正（2584.22→2587.91）</t>
         </is>
       </c>
+      <c r="Q5" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="30.4" customHeight="1">
       <c r="A6" s="23" t="n">
@@ -1138,6 +1159,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q6" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="43.59999999999999" customHeight="1">
       <c r="A7" s="23" t="n">
@@ -1218,6 +1244,11 @@
           <t>已修正（19.04%→10.28%，归母期末口径）</t>
         </is>
       </c>
+      <c r="Q7" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="43.59999999999999" customHeight="1">
       <c r="A8" s="23" t="n">
@@ -1298,6 +1329,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q8" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="56.8" customHeight="1">
       <c r="A9" s="23" t="n">
@@ -1378,6 +1414,11 @@
           <t>已修正（A2/A-/A→A2/A-/A-）+已换源（首页→惠誉公告）</t>
         </is>
       </c>
+      <c r="Q9" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="30.4" customHeight="1">
       <c r="A10" s="23" t="n">
@@ -1458,6 +1499,11 @@
           <t>保持（口径=经营现金净流量/营业收入，非营业总收入）</t>
         </is>
       </c>
+      <c r="Q10" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="30.4" customHeight="1">
       <c r="A11" s="23" t="n">
@@ -1538,6 +1584,11 @@
           <t>保持（口径已注明：营业总收入，与评级/同业一致）</t>
         </is>
       </c>
+      <c r="Q11" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="30.4" customHeight="1">
       <c r="A12" s="23" t="n">
@@ -1618,6 +1669,11 @@
           <t>已修正（197.63→195.94）</t>
         </is>
       </c>
+      <c r="Q12" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="30.4" customHeight="1">
       <c r="A13" s="23" t="n">
@@ -1698,6 +1754,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q13" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="30.4" customHeight="1">
       <c r="A14" s="23" t="n">
@@ -1778,6 +1839,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q14" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="43.59999999999999" customHeight="1">
       <c r="A15" s="23" t="n">
@@ -1854,6 +1920,11 @@
           <t>建议URL留空、数据保留、data_source注明平台名（与12家专利格一致）</t>
         </is>
       </c>
+      <c r="Q15" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="43.59999999999999" customHeight="1">
       <c r="A16" s="23" t="n">
@@ -1930,6 +2001,11 @@
           <t>已换源（URL留空、data_source改方法说明，与南方/联合/NTPC三格一致）</t>
         </is>
       </c>
+      <c r="Q16" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="83.19999999999999" customHeight="1">
       <c r="A17" s="23" t="n">
@@ -2010,6 +2086,11 @@
           <t>保持（A1实证；建议在来源补A2中电联名单URL）</t>
         </is>
       </c>
+      <c r="Q17" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="17.2" customHeight="1">
       <c r="A18" s="23" t="n">
@@ -2090,6 +2171,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q18" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="30.4" customHeight="1">
       <c r="A19" s="23" t="n">
@@ -2117,7 +2203,7 @@
       </c>
       <c r="F19" s="23" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>6.61</t>
         </is>
       </c>
       <c r="G19" s="23" t="inlineStr">
@@ -2147,27 +2233,32 @@
       </c>
       <c r="L19" s="24" t="inlineStr">
         <is>
-          <t>合并利润表：归属于母公司所有者的净利润6,149,372,255.99元(2025年度)；合并资产负债表：归属于母公司所有者权益合计93,705,345,921.44元(2025.12.31)</t>
+          <t>2025年度审计报告合并利润表：归属于母公司股东的净利润6,191,283,501.08元；合并资产负债表（续）归属于母公司所有者权益合计93,705,345,921.44元。</t>
         </is>
       </c>
       <c r="M19" s="24" t="inlineStr">
         <is>
-          <t>audit.pdf 合并利润表(报表第6页)；合并资产负债表(续)(报表第5页)</t>
+          <t>datang_audit.pdf 合并利润表（报告第6页/PDF第7页）、合并资产负债表（续）（报告第5页）</t>
         </is>
       </c>
       <c r="N19" s="24" t="inlineStr">
         <is>
-          <t>归母净利润61.49亿元(合并利润表报表第6页，印出6,149,372,255.99元)÷归母所有者权益937.05亿元(合并资产负债表报表第5页，印出93,705,345,921.44元,期末)=6.56%</t>
+          <t>ROE=61.9128亿元÷937.0535亿元=6.61%；原N列误引6,149,372,255.99元，经审计报告原表更正为6,191,283,501.08元。</t>
         </is>
       </c>
       <c r="O19" s="30" t="inlineStr">
         <is>
-          <t>不一致</t>
+          <t>不一致（2026外部回源已修正）</t>
         </is>
       </c>
       <c r="P19" s="23" t="inlineStr">
         <is>
-          <t>已修正(9.19%→6.56%)</t>
+          <t>已修正：6.56%→6.61%</t>
+        </is>
+      </c>
+      <c r="Q19" s="23" t="inlineStr">
+        <is>
+          <t>已修正</t>
         </is>
       </c>
     </row>
@@ -2250,6 +2341,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q20" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="17.2" customHeight="1">
       <c r="A21" s="23" t="n">
@@ -2330,6 +2426,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q21" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="17.2" customHeight="1">
       <c r="A22" s="23" t="n">
@@ -2410,6 +2511,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q22" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="17.2" customHeight="1">
       <c r="A23" s="23" t="n">
@@ -2490,6 +2596,11 @@
           <t>已修正(1395.32→1397.32)</t>
         </is>
       </c>
+      <c r="Q23" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="17.2" customHeight="1">
       <c r="A24" s="23" t="n">
@@ -2570,6 +2681,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q24" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="17.2" customHeight="1">
       <c r="A25" s="23" t="n">
@@ -2650,6 +2766,11 @@
           <t>已修正(371.13→371.66)</t>
         </is>
       </c>
+      <c r="Q25" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="17.2" customHeight="1">
       <c r="A26" s="23" t="n">
@@ -2730,6 +2851,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q26" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="17.2" customHeight="1">
       <c r="A27" s="23" t="n">
@@ -2810,6 +2936,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q27" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="17.2" customHeight="1">
       <c r="A28" s="23" t="n">
@@ -2890,6 +3021,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q28" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="17.2" customHeight="1">
       <c r="A29" s="23" t="n">
@@ -2970,6 +3106,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q29" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="17.2" customHeight="1">
       <c r="A30" s="23" t="n">
@@ -3046,6 +3187,11 @@
           <t>建议留空</t>
         </is>
       </c>
+      <c r="Q30" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="17.2" customHeight="1">
       <c r="A31" s="23" t="n">
@@ -3126,6 +3272,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q31" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="17.2" customHeight="1">
       <c r="A32" s="23" t="n">
@@ -3206,6 +3357,11 @@
           <t>保持(无国际评级)</t>
         </is>
       </c>
+      <c r="Q32" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="30.4" customHeight="1">
       <c r="A33" s="23" t="n">
@@ -3282,6 +3438,11 @@
           <t>建议URL留空、保留数值</t>
         </is>
       </c>
+      <c r="Q33" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="17.2" customHeight="1">
       <c r="A34" s="23" t="n">
@@ -3358,6 +3519,11 @@
           <t>保持(URL留空)</t>
         </is>
       </c>
+      <c r="Q34" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="30.4" customHeight="1">
       <c r="A35" s="23" t="n">
@@ -3438,6 +3604,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q35" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="17.2" customHeight="1">
       <c r="A36" s="23" t="n">
@@ -3518,6 +3689,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q36" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="17.2" customHeight="1">
       <c r="A37" s="23" t="n">
@@ -3545,7 +3721,7 @@
       </c>
       <c r="F37" s="23" t="inlineStr">
         <is>
-          <t>1870.50</t>
+          <t>1873.17</t>
         </is>
       </c>
       <c r="G37" s="23" t="inlineStr">
@@ -3575,27 +3751,32 @@
       </c>
       <c r="L37" s="24" t="inlineStr">
         <is>
-          <t>华电集团合并总资产口径(评级报告)</t>
+          <t>华电集团2026跟踪评级报告（中诚信）主要财务数据：2025年末合并资产总额13,093.47亿元。</t>
         </is>
       </c>
       <c r="M37" s="24" t="inlineStr">
         <is>
-          <t>rating.pdf 主要财务数据</t>
+          <t>huadian_rating.pdf 第4页主要财务数据</t>
         </is>
       </c>
       <c r="N37" s="24" t="inlineStr">
         <is>
-          <t>合并总资产折美元=1870.50亿美元</t>
+          <t>13,093.47亿元÷6.99=1,873.17亿美元；原1,870.50亿美元系误用7.0折算。</t>
         </is>
       </c>
       <c r="O37" s="25" t="inlineStr">
         <is>
-          <t>一致</t>
+          <t>不一致（2026外部回源已修正）</t>
         </is>
       </c>
       <c r="P37" s="23" t="inlineStr">
         <is>
-          <t>保持</t>
+          <t>已修正：1870.50→1873.17亿美元</t>
+        </is>
+      </c>
+      <c r="Q37" s="23" t="inlineStr">
+        <is>
+          <t>已修正</t>
         </is>
       </c>
     </row>
@@ -3678,6 +3859,11 @@
           <t>已修正(9.32%→13.92%)</t>
         </is>
       </c>
+      <c r="Q38" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="17.2" customHeight="1">
       <c r="A39" s="23" t="n">
@@ -3758,6 +3944,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q39" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="17.2" customHeight="1">
       <c r="A40" s="23" t="n">
@@ -3838,6 +4029,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q40" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="17.2" customHeight="1">
       <c r="A41" s="23" t="n">
@@ -3865,7 +4061,7 @@
       </c>
       <c r="F41" s="23" t="inlineStr">
         <is>
-          <t>27.85</t>
+          <t>27.38</t>
         </is>
       </c>
       <c r="G41" s="23" t="inlineStr">
@@ -3895,27 +4091,32 @@
       </c>
       <c r="L41" s="24" t="inlineStr">
         <is>
-          <t>经营净现金流854.43亿元；营业总收入3068.40亿元</t>
+          <t>华电集团2026跟踪评级报告：2025年经营活动现金流量净额854.43亿元、营业总收入3,120.32亿元。</t>
         </is>
       </c>
       <c r="M41" s="24" t="inlineStr">
         <is>
-          <t>rating.pdf/债券年报合并现金流量表</t>
+          <t>huadian_rating.pdf 第4页主要财务数据（合并现金流量表口径）</t>
         </is>
       </c>
       <c r="N41" s="24" t="inlineStr">
         <is>
-          <t>854.43亿元÷3068.40亿元=27.85%；底表27.38略低，按官方重算</t>
+          <t>854.43÷3,120.32=27.38%；原27.85%误以主营业务收入3,068.40亿元作分母，分母须与营业总收入口径一致。</t>
         </is>
       </c>
       <c r="O41" s="25" t="inlineStr">
         <is>
-          <t>一致</t>
+          <t>不一致（2026外部回源已修正）</t>
         </is>
       </c>
       <c r="P41" s="23" t="inlineStr">
         <is>
-          <t>已修正(27.38→27.85)</t>
+          <t>已修正：27.85%→27.38%</t>
+        </is>
+      </c>
+      <c r="Q41" s="23" t="inlineStr">
+        <is>
+          <t>已修正</t>
         </is>
       </c>
     </row>
@@ -3945,7 +4146,7 @@
       </c>
       <c r="F42" s="23" t="inlineStr">
         <is>
-          <t>438.97</t>
+          <t>446.40</t>
         </is>
       </c>
       <c r="G42" s="23" t="inlineStr">
@@ -3975,27 +4176,32 @@
       </c>
       <c r="L42" s="24" t="inlineStr">
         <is>
-          <t>营业总收入2025=3068.40亿元</t>
+          <t>华电集团2026跟踪评级报告合并利润表：2025年营业总收入3,120.32亿元（主营业务收入3,068.40亿元、营业收入3,089.09亿元）。</t>
         </is>
       </c>
       <c r="M42" s="24" t="inlineStr">
         <is>
-          <t>债券年报合并利润表</t>
+          <t>huadian_rating.pdf 第4页主表、第11页表6</t>
         </is>
       </c>
       <c r="N42" s="24" t="inlineStr">
         <is>
-          <t>3068.40亿元÷6.99=438.97亿美元；底表456.91偏高，修正</t>
+          <t>3,120.32÷6.99=446.40亿美元；原438.97亿美元误用主营业务收入3,068.40亿元，对标口径取集团营业总收入。</t>
         </is>
       </c>
       <c r="O42" s="30" t="inlineStr">
         <is>
-          <t>不一致</t>
+          <t>不一致（2026外部回源已修正）</t>
         </is>
       </c>
       <c r="P42" s="23" t="inlineStr">
         <is>
-          <t>已修正(456.91→438.97)</t>
+          <t>已修正：438.97→446.40亿美元</t>
+        </is>
+      </c>
+      <c r="Q42" s="23" t="inlineStr">
+        <is>
+          <t>已修正</t>
         </is>
       </c>
     </row>
@@ -4078,6 +4284,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q43" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="17.2" customHeight="1">
       <c r="A44" s="23" t="n">
@@ -4158,6 +4369,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q44" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="17.2" customHeight="1">
       <c r="A45" s="23" t="n">
@@ -4238,6 +4454,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q45" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="17.2" customHeight="1">
       <c r="A46" s="23" t="n">
@@ -4318,6 +4539,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q46" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="17.2" customHeight="1">
       <c r="A47" s="23" t="n">
@@ -4398,6 +4624,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q47" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="30.4" customHeight="1">
       <c r="A48" s="23" t="n">
@@ -4478,6 +4709,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q48" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="17.2" customHeight="1">
       <c r="A49" s="23" t="n">
@@ -4554,6 +4790,11 @@
           <t>建议URL留空</t>
         </is>
       </c>
+      <c r="Q49" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="17.2" customHeight="1">
       <c r="A50" s="23" t="n">
@@ -4630,6 +4871,11 @@
           <t>保持(URL留空)</t>
         </is>
       </c>
+      <c r="Q50" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="30.4" customHeight="1">
       <c r="A51" s="23" t="n">
@@ -4710,6 +4956,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q51" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="30.4" customHeight="1">
       <c r="A52" s="23" t="n">
@@ -4790,6 +5041,11 @@
           <t>建议留空</t>
         </is>
       </c>
+      <c r="Q52" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="17.2" customHeight="1">
       <c r="A53" s="23" t="n">
@@ -4870,6 +5126,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q53" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="17.2" customHeight="1">
       <c r="A54" s="23" t="n">
@@ -4950,6 +5211,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q54" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="30.4" customHeight="1">
       <c r="A55" s="23" t="n">
@@ -5030,6 +5296,11 @@
           <t>已修正(9.0%→9.27%)</t>
         </is>
       </c>
+      <c r="Q55" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="17.2" customHeight="1">
       <c r="A56" s="23" t="n">
@@ -5110,6 +5381,11 @@
           <t>已修正(12600→12541)</t>
         </is>
       </c>
+      <c r="Q56" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="17.2" customHeight="1">
       <c r="A57" s="23" t="n">
@@ -5190,6 +5466,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q57" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="17.2" customHeight="1">
       <c r="A58" s="23" t="n">
@@ -5270,6 +5551,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q58" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="17.2" customHeight="1">
       <c r="A59" s="23" t="n">
@@ -5350,6 +5636,11 @@
           <t>已修正(1009.81→1008.21)</t>
         </is>
       </c>
+      <c r="Q59" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="17.2" customHeight="1">
       <c r="A60" s="23" t="n">
@@ -5430,6 +5721,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q60" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="17.2" customHeight="1">
       <c r="A61" s="23" t="n">
@@ -5510,6 +5806,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q61" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="30.4" customHeight="1">
       <c r="A62" s="23" t="n">
@@ -5590,6 +5891,11 @@
           <t>已修正(约1.55%→约1.10%)</t>
         </is>
       </c>
+      <c r="Q62" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="17.2" customHeight="1">
       <c r="A63" s="23" t="n">
@@ -5670,6 +5976,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q63" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="30.4" customHeight="1">
       <c r="A64" s="23" t="n">
@@ -5750,6 +6061,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q64" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="17.2" customHeight="1">
       <c r="A65" s="23" t="n">
@@ -5830,6 +6146,11 @@
           <t>保持(无国际评级)</t>
         </is>
       </c>
+      <c r="Q65" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="17.2" customHeight="1">
       <c r="A66" s="23" t="n">
@@ -5906,6 +6227,11 @@
           <t>保持(URL留空)</t>
         </is>
       </c>
+      <c r="Q66" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="17.2" customHeight="1">
       <c r="A67" s="23" t="n">
@@ -5982,6 +6308,11 @@
           <t>保持(URL留空)</t>
         </is>
       </c>
+      <c r="Q67" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="30.4" customHeight="1">
       <c r="A68" s="23" t="n">
@@ -6062,6 +6393,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q68" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="30.4" customHeight="1">
       <c r="A69" s="23" t="n">
@@ -6142,6 +6478,11 @@
           <t>建议留空</t>
         </is>
       </c>
+      <c r="Q69" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="17.2" customHeight="1">
       <c r="A70" s="23" t="n">
@@ -6222,6 +6563,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q70" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="30.4" customHeight="1">
       <c r="A71" s="23" t="n">
@@ -6302,6 +6648,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q71" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="30.4" customHeight="1">
       <c r="A72" s="23" t="n">
@@ -6382,6 +6733,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q72" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="30.4" customHeight="1">
       <c r="A73" s="23" t="n">
@@ -6462,6 +6818,11 @@
           <t>已修正(577.28→578.11)</t>
         </is>
       </c>
+      <c r="Q73" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="30.4" customHeight="1">
       <c r="A74" s="23" t="n">
@@ -6542,6 +6903,11 @@
           <t>已修正(2817.32→2821.35)</t>
         </is>
       </c>
+      <c r="Q74" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="30.4" customHeight="1">
       <c r="A75" s="23" t="n">
@@ -6622,6 +6988,11 @@
           <t>已修正(7.1%→7.30%)</t>
         </is>
       </c>
+      <c r="Q75" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="30.4" customHeight="1">
       <c r="A76" s="23" t="n">
@@ -6702,6 +7073,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q76" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="30.4" customHeight="1">
       <c r="A77" s="23" t="n">
@@ -6782,6 +7158,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q77" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="30.4" customHeight="1">
       <c r="A78" s="23" t="n">
@@ -6862,6 +7243,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q78" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="30.4" customHeight="1">
       <c r="A79" s="23" t="n">
@@ -6942,6 +7328,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q79" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="30.4" customHeight="1">
       <c r="A80" s="23" t="n">
@@ -7022,6 +7413,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q80" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="30.4" customHeight="1">
       <c r="A81" s="23" t="n">
@@ -7102,6 +7498,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q81" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="17.2" customHeight="1">
       <c r="A82" s="23" t="n">
@@ -7182,6 +7583,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q82" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="17.2" customHeight="1">
       <c r="A83" s="23" t="n">
@@ -7262,6 +7668,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q83" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="17.2" customHeight="1">
       <c r="A84" s="23" t="n">
@@ -7342,6 +7753,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q84" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="17.2" customHeight="1">
       <c r="A85" s="23" t="n">
@@ -7418,6 +7834,11 @@
           <t>建议URL留空</t>
         </is>
       </c>
+      <c r="Q85" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="17.2" customHeight="1">
       <c r="A86" s="23" t="n">
@@ -7494,6 +7915,11 @@
           <t>保持(URL留空)</t>
         </is>
       </c>
+      <c r="Q86" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="30.4" customHeight="1">
       <c r="A87" s="23" t="n">
@@ -7574,6 +8000,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q87" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="30.4" customHeight="1">
       <c r="A88" s="23" t="n">
@@ -7601,7 +8032,7 @@
       </c>
       <c r="F88" s="23" t="inlineStr">
         <is>
-          <t>2163.44</t>
+          <t>2166.54</t>
         </is>
       </c>
       <c r="G88" s="23" t="inlineStr">
@@ -7631,27 +8062,32 @@
       </c>
       <c r="L88" s="24" t="inlineStr">
         <is>
-          <t>2025末资产总额1.52万亿元。</t>
+          <t>中诚信三峡集团2026跟踪评级报告合并财务数据：2025年末资产总计15,144.11亿元。</t>
         </is>
       </c>
       <c r="M88" s="24" t="inlineStr">
         <is>
-          <t>评级报告财务概况</t>
+          <t>ctg_rating.pdf 第5、13、18页（集团合并主表；第10、17页862.42为旗下长江电力，勿顶替）</t>
         </is>
       </c>
       <c r="N88" s="24" t="inlineStr">
         <is>
-          <t>资产1.52万亿元÷6.99=2174.5亿美元≈2163.44。</t>
+          <t>15,144.11÷6.99=2,166.54亿美元；原2,163.44误用7.0折算。</t>
         </is>
       </c>
       <c r="O88" s="25" t="inlineStr">
         <is>
-          <t>一致</t>
+          <t>不一致（2026外部回源已修正）</t>
         </is>
       </c>
       <c r="P88" s="23" t="inlineStr">
         <is>
-          <t>保持</t>
+          <t>已修正：2163.44→2166.54亿美元</t>
+        </is>
+      </c>
+      <c r="Q88" s="23" t="inlineStr">
+        <is>
+          <t>已修正</t>
         </is>
       </c>
     </row>
@@ -7734,6 +8170,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q89" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="17.2" customHeight="1">
       <c r="A90" s="23" t="n">
@@ -7761,7 +8202,7 @@
       </c>
       <c r="F90" s="23" t="inlineStr">
         <is>
-          <t>232.50</t>
+          <t>228.42</t>
         </is>
       </c>
       <c r="G90" s="23" t="inlineStr">
@@ -7791,25 +8232,30 @@
       </c>
       <c r="L90" s="24" t="inlineStr">
         <is>
-          <t>2025年营业总收入约1625.17亿元。</t>
+          <t>三峡集团2025年度审计报告/中诚信2026跟踪评级：2025年营业总收入1,596.66亿元（2024年为1,625.17亿元）。</t>
         </is>
       </c>
       <c r="M90" s="24" t="inlineStr">
         <is>
-          <t>合并利润表</t>
+          <t>ctg_rating.pdf 第5、13页（集团合并口径，非长江电力）</t>
         </is>
       </c>
       <c r="N90" s="24" t="inlineStr">
         <is>
-          <t>营收1625.17亿元÷6.99=232.50亿美元；底表227.53偏低。</t>
+          <t>1,596.66÷6.99=228.42亿美元；原232.50亿美元误用2024年1,625.17亿元。</t>
         </is>
       </c>
       <c r="O90" s="25" t="inlineStr">
         <is>
-          <t>一致</t>
+          <t>不一致（2026外部回源已修正）</t>
         </is>
       </c>
       <c r="P90" s="23" t="inlineStr">
+        <is>
+          <t>已修正：232.50→228.42亿美元（年份错）</t>
+        </is>
+      </c>
+      <c r="Q90" s="23" t="inlineStr">
         <is>
           <t>已修正</t>
         </is>
@@ -7894,6 +8340,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q91" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="30.4" customHeight="1">
       <c r="A92" s="23" t="n">
@@ -7974,6 +8425,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q92" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="30.4" customHeight="1">
       <c r="A93" s="23" t="n">
@@ -8054,6 +8510,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q93" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="30.4" customHeight="1">
       <c r="A94" s="23" t="n">
@@ -8134,6 +8595,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q94" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="30.4" customHeight="1">
       <c r="A95" s="23" t="n">
@@ -8214,6 +8680,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q95" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="30.4" customHeight="1">
       <c r="A96" s="23" t="n">
@@ -8294,6 +8765,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q96" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="17.2" customHeight="1">
       <c r="A97" s="23" t="n">
@@ -8374,6 +8850,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q97" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="17.2" customHeight="1">
       <c r="A98" s="23" t="n">
@@ -8454,6 +8935,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q98" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="30.4" customHeight="1">
       <c r="A99" s="23" t="n">
@@ -8534,6 +9020,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q99" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="30.4" customHeight="1">
       <c r="A100" s="23" t="n">
@@ -8614,6 +9105,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q100" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="43.59999999999999" customHeight="1">
       <c r="A101" s="23" t="n">
@@ -8690,6 +9186,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q101" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="30.4" customHeight="1">
       <c r="A102" s="23" t="n">
@@ -8766,6 +9267,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q102" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="17.2" customHeight="1">
       <c r="A103" s="23" t="n">
@@ -8846,6 +9352,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q103" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="17.2" customHeight="1">
       <c r="A104" s="23" t="n">
@@ -8926,6 +9437,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q104" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="17.2" customHeight="1">
       <c r="A105" s="23" t="n">
@@ -8953,7 +9469,7 @@
       </c>
       <c r="F105" s="23" t="inlineStr">
         <is>
-          <t>1656.42</t>
+          <t>1658.79</t>
         </is>
       </c>
       <c r="G105" s="23" t="inlineStr">
@@ -8983,27 +9499,32 @@
       </c>
       <c r="L105" s="24" t="inlineStr">
         <is>
-          <t>中广核集团2025末资产总额11594.93亿元</t>
+          <t>中国广核集团2025年度报告：2025年末合并资产总额11,594.93亿元（集团口径，非中广核电力）。</t>
         </is>
       </c>
       <c r="M105" s="24" t="inlineStr">
         <is>
-          <t>cnstock 2025年度报告摘要</t>
+          <t>cnstock 2025年度报告摘要（集团口径）</t>
         </is>
       </c>
       <c r="N105" s="24" t="inlineStr">
         <is>
-          <t>11594.93亿元÷6.99=1658.79亿美元；底表1656.42差0.14%</t>
+          <t>11,594.93÷6.99=1,658.79亿美元；原1,656.42误用7.0折算。</t>
         </is>
       </c>
       <c r="O105" s="25" t="inlineStr">
         <is>
-          <t>一致</t>
+          <t>不一致（2026外部回源已修正）</t>
         </is>
       </c>
       <c r="P105" s="23" t="inlineStr">
         <is>
-          <t>保持</t>
+          <t>已修正：1656.42→1658.79亿美元</t>
+        </is>
+      </c>
+      <c r="Q105" s="23" t="inlineStr">
+        <is>
+          <t>已修正</t>
         </is>
       </c>
     </row>
@@ -9086,6 +9607,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q106" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="30.4" customHeight="1">
       <c r="A107" s="23" t="n">
@@ -9166,6 +9692,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q107" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="17.2" customHeight="1">
       <c r="A108" s="23" t="n">
@@ -9242,6 +9773,11 @@
           <t>建议URL留空</t>
         </is>
       </c>
+      <c r="Q108" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="17.2" customHeight="1">
       <c r="A109" s="23" t="n">
@@ -9318,6 +9854,11 @@
           <t>保持(URL留空)</t>
         </is>
       </c>
+      <c r="Q109" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="30.4" customHeight="1">
       <c r="A110" s="23" t="n">
@@ -9398,6 +9939,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q110" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="30.4" customHeight="1">
       <c r="A111" s="23" t="n">
@@ -9478,6 +10024,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q111" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="30.4" customHeight="1">
       <c r="A112" s="23" t="n">
@@ -9505,7 +10056,7 @@
       </c>
       <c r="F112" s="23" t="inlineStr">
         <is>
-          <t>467.71</t>
+          <t>468.38</t>
         </is>
       </c>
       <c r="G112" s="23" t="inlineStr">
@@ -9535,27 +10086,32 @@
       </c>
       <c r="L112" s="24" t="inlineStr">
         <is>
-          <t>2025末总资产约3269亿元。</t>
+          <t>中诚信广东能源2026跟踪评级报告合并资产负债表：2025年末资产总计327,394,053,355.66元（3,273.94亿元）。</t>
         </is>
       </c>
       <c r="M112" s="24" t="inlineStr">
         <is>
-          <t>评级报告财务概况</t>
+          <t>geg_rating2026.pdf 第4页同业表、第18页合并资产负债表</t>
         </is>
       </c>
       <c r="N112" s="24" t="inlineStr">
         <is>
-          <t>总资产约3269亿元÷6.99=467.71亿美元。</t>
+          <t>3,273.94÷6.99=468.38亿美元；原467.71按约3,269亿元折算，差0.14%。</t>
         </is>
       </c>
       <c r="O112" s="25" t="inlineStr">
         <is>
-          <t>一致</t>
+          <t>不一致（2026外部回源已修正）</t>
         </is>
       </c>
       <c r="P112" s="23" t="inlineStr">
         <is>
-          <t>保持</t>
+          <t>已修正：467.71→468.38亿美元</t>
+        </is>
+      </c>
+      <c r="Q112" s="23" t="inlineStr">
+        <is>
+          <t>已修正</t>
         </is>
       </c>
     </row>
@@ -9585,7 +10141,7 @@
       </c>
       <c r="F113" s="23" t="inlineStr">
         <is>
-          <t>30.18</t>
+          <t>30.64</t>
         </is>
       </c>
       <c r="G113" s="23" t="inlineStr">
@@ -9615,27 +10171,32 @@
       </c>
       <c r="L113" s="24" t="inlineStr">
         <is>
-          <t>2025年EBITDA约211亿元。</t>
+          <t>中诚信广东能源2026跟踪评级报告：2025年EBITDA 214.17亿元。</t>
         </is>
       </c>
       <c r="M113" s="24" t="inlineStr">
         <is>
-          <t>评级报告</t>
+          <t>geg_rating2026.pdf 第4、13页（财务摘要）</t>
         </is>
       </c>
       <c r="N113" s="24" t="inlineStr">
         <is>
-          <t>EBITDA约211亿元÷6.99=30.18亿美元。</t>
+          <t>214.17÷6.99=30.64亿美元；原30.18按约211亿元折算。</t>
         </is>
       </c>
       <c r="O113" s="25" t="inlineStr">
         <is>
-          <t>一致</t>
+          <t>不一致（2026外部回源已修正）</t>
         </is>
       </c>
       <c r="P113" s="23" t="inlineStr">
         <is>
-          <t>保持</t>
+          <t>已修正：30.18→30.64亿美元</t>
+        </is>
+      </c>
+      <c r="Q113" s="23" t="inlineStr">
+        <is>
+          <t>已修正</t>
         </is>
       </c>
     </row>
@@ -9718,6 +10279,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q114" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="17.2" customHeight="1">
       <c r="A115" s="23" t="n">
@@ -9745,7 +10311,7 @@
       </c>
       <c r="F115" s="23" t="inlineStr">
         <is>
-          <t>119.97</t>
+          <t>118.04</t>
         </is>
       </c>
       <c r="G115" s="23" t="inlineStr">
@@ -9775,25 +10341,30 @@
       </c>
       <c r="L115" s="24" t="inlineStr">
         <is>
-          <t>2025年营业总收入约837.60亿元。</t>
+          <t>中诚信广东能源2026跟踪评级报告合并利润表及同业比较表：2025年营业总收入825.13亿元（2024年837.60亿元、2023年835.94亿元）。</t>
         </is>
       </c>
       <c r="M115" s="24" t="inlineStr">
         <is>
-          <t>合并利润表</t>
+          <t>geg_rating2026.pdf 第4页同业表、第27页合并利润表</t>
         </is>
       </c>
       <c r="N115" s="24" t="inlineStr">
         <is>
-          <t>营收837.60亿元÷6.99=119.97亿美元；底表117.88。</t>
+          <t>825.13÷6.99=118.04亿美元；原119.97亿美元误用2024年837.60亿元。</t>
         </is>
       </c>
       <c r="O115" s="25" t="inlineStr">
         <is>
-          <t>一致</t>
+          <t>不一致（2026外部回源已修正）</t>
         </is>
       </c>
       <c r="P115" s="23" t="inlineStr">
+        <is>
+          <t>已修正：119.97→118.04亿美元（年份错）</t>
+        </is>
+      </c>
+      <c r="Q115" s="23" t="inlineStr">
         <is>
           <t>已修正</t>
         </is>
@@ -9878,6 +10449,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q116" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="30.4" customHeight="1">
       <c r="A117" s="23" t="n">
@@ -9958,6 +10534,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q117" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="17.2" customHeight="1">
       <c r="A118" s="23" t="n">
@@ -10038,6 +10619,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q118" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="17.2" customHeight="1">
       <c r="A119" s="23" t="n">
@@ -10118,6 +10704,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q119" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="30.4" customHeight="1">
       <c r="A120" s="23" t="n">
@@ -10198,6 +10789,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q120" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="17.2" customHeight="1">
       <c r="A121" s="23" t="n">
@@ -10274,6 +10870,11 @@
           <t>数值留空、不参与2025年国际信用评级计分；品牌卓著维度按营业收入、资产总额两项可取得指标均分（综合第20位，待取得有效评级后上修）</t>
         </is>
       </c>
+      <c r="Q121" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="43.59999999999999" customHeight="1">
       <c r="A122" s="23" t="n">
@@ -10350,6 +10951,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q122" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="30.4" customHeight="1">
       <c r="A123" s="23" t="n">
@@ -10426,6 +11032,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q123" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="17.2" customHeight="1">
       <c r="A124" s="23" t="n">
@@ -10506,6 +11117,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q124" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="30.4" customHeight="1">
       <c r="A125" s="23" t="n">
@@ -10586,6 +11202,11 @@
           <t>建议留空</t>
         </is>
       </c>
+      <c r="Q125" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="17.2" customHeight="1">
       <c r="A126" s="23" t="n">
@@ -10666,6 +11287,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q126" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="30.4" customHeight="1">
       <c r="A127" s="23" t="n">
@@ -10746,6 +11372,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q127" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="30.4" customHeight="1">
       <c r="A128" s="23" t="n">
@@ -10826,6 +11457,11 @@
           <t>已修正</t>
         </is>
       </c>
+      <c r="Q128" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="30.4" customHeight="1">
       <c r="A129" s="23" t="n">
@@ -10906,6 +11542,11 @@
           <t>已修正</t>
         </is>
       </c>
+      <c r="Q129" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="30.4" customHeight="1">
       <c r="A130" s="23" t="n">
@@ -10986,6 +11627,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q130" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="30.4" customHeight="1">
       <c r="A131" s="23" t="n">
@@ -11066,6 +11712,11 @@
           <t>已修正</t>
         </is>
       </c>
+      <c r="Q131" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="132" ht="30.4" customHeight="1">
       <c r="A132" s="23" t="n">
@@ -11146,6 +11797,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q132" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="30.4" customHeight="1">
       <c r="A133" s="23" t="n">
@@ -11226,6 +11882,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q133" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="30.4" customHeight="1">
       <c r="A134" s="23" t="n">
@@ -11306,6 +11967,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q134" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="135" ht="30.4" customHeight="1">
       <c r="A135" s="23" t="n">
@@ -11386,6 +12052,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q135" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="136" ht="30.4" customHeight="1">
       <c r="A136" s="23" t="n">
@@ -11466,6 +12137,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q136" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="137" ht="30.4" customHeight="1">
       <c r="A137" s="23" t="n">
@@ -11546,6 +12222,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q137" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="138" ht="17.2" customHeight="1">
       <c r="A138" s="23" t="n">
@@ -11626,6 +12307,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q138" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="139" ht="43.59999999999999" customHeight="1">
       <c r="A139" s="23" t="n">
@@ -11702,6 +12388,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q139" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="140" ht="30.4" customHeight="1">
       <c r="A140" s="23" t="n">
@@ -11778,6 +12469,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q140" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="141" ht="17.2" customHeight="1">
       <c r="A141" s="23" t="n">
@@ -11858,6 +12554,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q141" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="142" ht="30.4" customHeight="1">
       <c r="A142" s="23" t="n">
@@ -11938,6 +12639,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q142" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="143" ht="30.4" customHeight="1">
       <c r="A143" s="23" t="n">
@@ -12018,6 +12724,11 @@
           <t>已修正</t>
         </is>
       </c>
+      <c r="Q143" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="144" ht="30.4" customHeight="1">
       <c r="A144" s="23" t="n">
@@ -12098,6 +12809,11 @@
           <t>已修正</t>
         </is>
       </c>
+      <c r="Q144" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="145" ht="30.4" customHeight="1">
       <c r="A145" s="23" t="n">
@@ -12178,6 +12894,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q145" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="146" ht="30.4" customHeight="1">
       <c r="A146" s="23" t="n">
@@ -12258,6 +12979,11 @@
           <t>已修正</t>
         </is>
       </c>
+      <c r="Q146" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="147" ht="30.4" customHeight="1">
       <c r="A147" s="23" t="n">
@@ -12338,6 +13064,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q147" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="148" ht="30.4" customHeight="1">
       <c r="A148" s="23" t="n">
@@ -12418,6 +13149,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q148" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="149" ht="17.2" customHeight="1">
       <c r="A149" s="23" t="n">
@@ -12498,6 +13234,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q149" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="150" ht="17.2" customHeight="1">
       <c r="A150" s="23" t="n">
@@ -12578,6 +13319,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q150" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="151" ht="43.59999999999999" customHeight="1">
       <c r="A151" s="23" t="n">
@@ -12654,6 +13400,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q151" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="152" ht="30.4" customHeight="1">
       <c r="A152" s="23" t="n">
@@ -12730,6 +13481,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q152" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="153" ht="17.2" customHeight="1">
       <c r="A153" s="23" t="n">
@@ -12810,6 +13566,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q153" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="154" ht="30.4" customHeight="1">
       <c r="A154" s="23" t="n">
@@ -12890,6 +13651,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q154" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="155" ht="30.4" customHeight="1">
       <c r="A155" s="23" t="n">
@@ -12970,6 +13736,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q155" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="156" ht="30.4" customHeight="1">
       <c r="A156" s="23" t="n">
@@ -13050,6 +13821,11 @@
           <t>已修正</t>
         </is>
       </c>
+      <c r="Q156" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="157" ht="30.4" customHeight="1">
       <c r="A157" s="23" t="n">
@@ -13130,6 +13906,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q157" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="158" ht="30.4" customHeight="1">
       <c r="A158" s="23" t="n">
@@ -13210,6 +13991,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q158" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="159" ht="30.4" customHeight="1">
       <c r="A159" s="23" t="n">
@@ -13290,6 +14076,11 @@
           <t>已修正</t>
         </is>
       </c>
+      <c r="Q159" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="160" ht="30.4" customHeight="1">
       <c r="A160" s="23" t="n">
@@ -13370,6 +14161,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q160" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="161" ht="30.4" customHeight="1">
       <c r="A161" s="23" t="n">
@@ -13450,6 +14246,11 @@
           <t>已修正</t>
         </is>
       </c>
+      <c r="Q161" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="162" ht="30.4" customHeight="1">
       <c r="A162" s="23" t="n">
@@ -13530,6 +14331,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q162" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="163" ht="30.4" customHeight="1">
       <c r="A163" s="23" t="n">
@@ -13610,6 +14416,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q163" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="164" ht="30.4" customHeight="1">
       <c r="A164" s="23" t="n">
@@ -13690,6 +14501,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q164" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="165" ht="30.4" customHeight="1">
       <c r="A165" s="23" t="n">
@@ -13770,6 +14586,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q165" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="166" ht="30.4" customHeight="1">
       <c r="A166" s="23" t="n">
@@ -13850,6 +14671,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q166" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="167" ht="43.59999999999999" customHeight="1">
       <c r="A167" s="23" t="n">
@@ -13926,6 +14752,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q167" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="168" ht="30.4" customHeight="1">
       <c r="A168" s="23" t="n">
@@ -14002,6 +14833,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q168" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="169" ht="30.4" customHeight="1">
       <c r="A169" s="23" t="n">
@@ -14082,6 +14918,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q169" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="170" ht="30.4" customHeight="1">
       <c r="A170" s="23" t="n">
@@ -14162,6 +15003,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q170" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="171" ht="30.4" customHeight="1">
       <c r="A171" s="23" t="n">
@@ -14242,6 +15088,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q171" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="172" ht="30.4" customHeight="1">
       <c r="A172" s="23" t="n">
@@ -14322,6 +15173,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q172" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="173" ht="30.4" customHeight="1">
       <c r="A173" s="23" t="n">
@@ -14402,6 +15258,11 @@
           <t>已修正</t>
         </is>
       </c>
+      <c r="Q173" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="174" ht="30.4" customHeight="1">
       <c r="A174" s="23" t="n">
@@ -14482,6 +15343,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q174" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="175" ht="30.4" customHeight="1">
       <c r="A175" s="23" t="n">
@@ -14562,6 +15428,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q175" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="176" ht="30.4" customHeight="1">
       <c r="A176" s="23" t="n">
@@ -14642,6 +15513,11 @@
           <t>已修正</t>
         </is>
       </c>
+      <c r="Q176" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="177" ht="30.4" customHeight="1">
       <c r="A177" s="23" t="n">
@@ -14722,6 +15598,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q177" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="178" ht="30.4" customHeight="1">
       <c r="A178" s="23" t="n">
@@ -14802,6 +15683,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q178" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="179" ht="30.4" customHeight="1">
       <c r="A179" s="23" t="n">
@@ -14882,6 +15768,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q179" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="180" ht="17.2" customHeight="1">
       <c r="A180" s="23" t="n">
@@ -14962,6 +15853,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q180" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="181" ht="43.59999999999999" customHeight="1">
       <c r="A181" s="23" t="n">
@@ -15038,6 +15934,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q181" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="182" ht="30.4" customHeight="1">
       <c r="A182" s="23" t="n">
@@ -15114,6 +16015,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q182" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="183" ht="17.2" customHeight="1">
       <c r="A183" s="23" t="n">
@@ -15194,6 +16100,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q183" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="184" ht="30.4" customHeight="1">
       <c r="A184" s="23" t="n">
@@ -15274,6 +16185,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q184" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="185" ht="30.4" customHeight="1">
       <c r="A185" s="23" t="n">
@@ -15352,6 +16268,11 @@
           <t>保持4683.0（accounting gross口径已确认）</t>
         </is>
       </c>
+      <c r="Q185" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="186" ht="30.4" customHeight="1">
       <c r="A186" s="23" t="n">
@@ -15432,6 +16353,11 @@
           <t>已修正</t>
         </is>
       </c>
+      <c r="Q186" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="187" ht="30.4" customHeight="1">
       <c r="A187" s="23" t="n">
@@ -15510,6 +16436,11 @@
           <t>保持1223.4（gross）</t>
         </is>
       </c>
+      <c r="Q187" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="188" ht="17.2" customHeight="1">
       <c r="A188" s="23" t="n">
@@ -15590,6 +16521,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q188" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="189" ht="43.59999999999999" customHeight="1">
       <c r="A189" s="23" t="n">
@@ -15668,6 +16604,11 @@
           <t>海外3151.3→3172.5（accounting gross两法互证）</t>
         </is>
       </c>
+      <c r="Q189" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="190" ht="30.4" customHeight="1">
       <c r="A190" s="23" t="n">
@@ -15748,6 +16689,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q190" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="191" ht="30.4" customHeight="1">
       <c r="A191" s="23" t="n">
@@ -15828,6 +16774,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q191" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="192" ht="43.59999999999999" customHeight="1">
       <c r="A192" s="23" t="n">
@@ -15908,6 +16859,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q192" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="193" ht="17.2" customHeight="1">
       <c r="A193" s="23" t="n">
@@ -15984,6 +16940,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q193" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="194" ht="30.4" customHeight="1">
       <c r="A194" s="23" t="n">
@@ -16064,6 +17025,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q194" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="195" ht="30.4" customHeight="1">
       <c r="A195" s="23" t="n">
@@ -16142,6 +17108,11 @@
           <t>保持45.5%（gross）</t>
         </is>
       </c>
+      <c r="Q195" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="196" ht="30.4" customHeight="1">
       <c r="A196" s="23" t="n">
@@ -16220,6 +17191,11 @@
           <t>41.4→41.3（gross精确取整）</t>
         </is>
       </c>
+      <c r="Q196" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="197" ht="17.2" customHeight="1">
       <c r="A197" s="23" t="n">
@@ -16300,6 +17276,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q197" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="198" ht="30.4" customHeight="1">
       <c r="A198" s="23" t="n">
@@ -16380,6 +17361,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q198" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="199" ht="30.4" customHeight="1">
       <c r="A199" s="23" t="n">
@@ -16460,6 +17446,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q199" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="200" ht="30.4" customHeight="1">
       <c r="A200" s="23" t="n">
@@ -16538,6 +17529,11 @@
           <t>76.5(并表/emission-free)→72.8（gross）</t>
         </is>
       </c>
+      <c r="Q200" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="201" ht="30.4" customHeight="1">
       <c r="A201" s="23" t="n">
@@ -16618,6 +17614,11 @@
           <t>已修正</t>
         </is>
       </c>
+      <c r="Q201" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="202" ht="30.4" customHeight="1">
       <c r="A202" s="23" t="n">
@@ -16698,6 +17699,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q202" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="203" ht="30.4" customHeight="1">
       <c r="A203" s="23" t="n">
@@ -16776,6 +17782,11 @@
           <t>保持9280（已确认含权益gross口径并注明）</t>
         </is>
       </c>
+      <c r="Q203" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="204" ht="30.4" customHeight="1">
       <c r="A204" s="23" t="n">
@@ -16856,6 +17867,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q204" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="205" ht="17.2" customHeight="1">
       <c r="A205" s="23" t="n">
@@ -16936,6 +17952,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q205" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="206" ht="30.4" customHeight="1">
       <c r="A206" s="23" t="n">
@@ -17014,6 +18035,11 @@
           <t>5884.2(并表)→6460（gross含JV）</t>
         </is>
       </c>
+      <c r="Q206" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="207" ht="30.4" customHeight="1">
       <c r="A207" s="23" t="n">
@@ -17094,6 +18120,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q207" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="208" ht="30.4" customHeight="1">
       <c r="A208" s="23" t="n">
@@ -17174,6 +18205,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q208" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="209" ht="43.59999999999999" customHeight="1">
       <c r="A209" s="23" t="n">
@@ -17254,6 +18290,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q209" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="210" ht="17.2" customHeight="1">
       <c r="A210" s="23" t="n">
@@ -17330,6 +18371,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q210" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="211" ht="30.4" customHeight="1">
       <c r="A211" s="23" t="n">
@@ -17410,6 +18456,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q211" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="212" ht="30.4" customHeight="1">
       <c r="A212" s="23" t="n">
@@ -17488,6 +18539,11 @@
           <t>82.2(并表净)→83.5（gross）</t>
         </is>
       </c>
+      <c r="Q212" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="213" ht="30.4" customHeight="1">
       <c r="A213" s="23" t="n">
@@ -17568,6 +18624,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q213" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="214" ht="30.4" customHeight="1">
       <c r="A214" s="23" t="n">
@@ -17648,6 +18709,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q214" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="215" ht="30.4" customHeight="1">
       <c r="A215" s="23" t="n">
@@ -17726,6 +18792,11 @@
           <t>1861.0(并表净)→2003（gross含JV）</t>
         </is>
       </c>
+      <c r="Q215" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="216" ht="30.4" customHeight="1">
       <c r="A216" s="23" t="n">
@@ -17806,6 +18877,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q216" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="217" ht="17.2" customHeight="1">
       <c r="A217" s="23" t="n">
@@ -17886,6 +18962,11 @@
           <t>已修正</t>
         </is>
       </c>
+      <c r="Q217" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="218" ht="17.2" customHeight="1">
       <c r="A218" s="23" t="n">
@@ -17966,6 +19047,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q218" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="219" ht="30.4" customHeight="1">
       <c r="A219" s="23" t="n">
@@ -18046,6 +19132,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q219" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="220" ht="30.4" customHeight="1">
       <c r="A220" s="23" t="n">
@@ -18126,6 +19217,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q220" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="221" ht="30.4" customHeight="1">
       <c r="A221" s="23" t="n">
@@ -18206,6 +19302,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q221" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="222" ht="30.4" customHeight="1">
       <c r="A222" s="23" t="n">
@@ -18284,6 +19385,11 @@
           <t>net 5834.3→gross下界7200.6（官方电厂配对零估算；另504MW权益风光仅披露份额未gross up，故略低估）</t>
         </is>
       </c>
+      <c r="Q222" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="223" ht="30.4" customHeight="1">
       <c r="A223" s="23" t="n">
@@ -18360,6 +19466,11 @@
           <t>net 1290.4清空，gross发电量留空（宁少而真）</t>
         </is>
       </c>
+      <c r="Q223" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="224" ht="17.2" customHeight="1">
       <c r="A224" s="23" t="n">
@@ -18440,6 +19551,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q224" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="225" ht="30.4" customHeight="1">
       <c r="A225" s="23" t="n">
@@ -18518,6 +19634,11 @@
           <t>net 2489.6→gross下界3653.9</t>
         </is>
       </c>
+      <c r="Q225" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="226" ht="17.2" customHeight="1">
       <c r="A226" s="23" t="n">
@@ -18598,6 +19719,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q226" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="227" ht="17.2" customHeight="1">
       <c r="A227" s="23" t="n">
@@ -18678,6 +19804,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q227" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="228" ht="43.59999999999999" customHeight="1">
       <c r="A228" s="23" t="n">
@@ -18758,6 +19889,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q228" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="229" ht="17.2" customHeight="1">
       <c r="A229" s="23" t="n">
@@ -18834,6 +19970,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q229" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="230" ht="30.4" customHeight="1">
       <c r="A230" s="23" t="n">
@@ -18912,6 +20053,11 @@
           <t>net 84.6→gross 86.5（下界口径）</t>
         </is>
       </c>
+      <c r="Q230" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="231" ht="30.4" customHeight="1">
       <c r="A231" s="23" t="n">
@@ -18988,6 +20134,11 @@
           <t>net 85.0清空，gross非化石发电占比留空</t>
         </is>
       </c>
+      <c r="Q231" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="232" ht="30.4" customHeight="1">
       <c r="A232" s="23" t="n">
@@ -19068,6 +20219,11 @@
           <t>已修正</t>
         </is>
       </c>
+      <c r="Q232" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="233" ht="30.4" customHeight="1">
       <c r="A233" s="23" t="n">
@@ -19148,6 +20304,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q233" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="234" ht="30.4" customHeight="1">
       <c r="A234" s="23" t="n">
@@ -19228,6 +20389,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q234" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="235" ht="30.4" customHeight="1">
       <c r="A235" s="23" t="n">
@@ -19308,6 +20474,11 @@
           <t>已修正</t>
         </is>
       </c>
+      <c r="Q235" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="236" ht="30.4" customHeight="1">
       <c r="A236" s="23" t="n">
@@ -19388,6 +20559,11 @@
           <t>已修正</t>
         </is>
       </c>
+      <c r="Q236" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="237" ht="17.2" customHeight="1">
       <c r="A237" s="23" t="n">
@@ -19468,6 +20644,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q237" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="238" ht="17.2" customHeight="1">
       <c r="A238" s="23" t="n">
@@ -19546,6 +20727,11 @@
           <t>5150(net取整)→5155（并表gross）</t>
         </is>
       </c>
+      <c r="Q238" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="239" ht="30.4" customHeight="1">
       <c r="A239" s="23" t="n">
@@ -19626,6 +20812,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q239" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="240" ht="17.2" customHeight="1">
       <c r="A240" s="23" t="n">
@@ -19706,6 +20897,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q240" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="241" ht="30.4" customHeight="1">
       <c r="A241" s="23" t="n">
@@ -19784,6 +20980,11 @@
           <t>net 12603→并表gross 11820</t>
         </is>
       </c>
+      <c r="Q241" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="242" ht="30.4" customHeight="1">
       <c r="A242" s="23" t="n">
@@ -19864,6 +21065,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q242" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="243" ht="30.4" customHeight="1">
       <c r="A243" s="23" t="n">
@@ -19944,6 +21150,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q243" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="244" ht="30.4" customHeight="1">
       <c r="A244" s="23" t="n">
@@ -20024,6 +21235,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q244" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="245" ht="30.4" customHeight="1">
       <c r="A245" s="23" t="n">
@@ -20104,6 +21320,11 @@
           <t>已修正</t>
         </is>
       </c>
+      <c r="Q245" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="246" ht="17.2" customHeight="1">
       <c r="A246" s="23" t="n">
@@ -20184,6 +21405,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q246" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="247" ht="30.4" customHeight="1">
       <c r="A247" s="23" t="n">
@@ -20260,6 +21486,11 @@
           <t>net 3120.9清空，gross海外装机留空（宁少而真）</t>
         </is>
       </c>
+      <c r="Q247" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="248" ht="43.59999999999999" customHeight="1">
       <c r="A248" s="23" t="n">
@@ -20340,6 +21571,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q248" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="249" ht="17.2" customHeight="1">
       <c r="A249" s="23" t="n">
@@ -20416,6 +21652,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q249" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="250" ht="30.4" customHeight="1">
       <c r="A250" s="23" t="n">
@@ -20494,6 +21735,11 @@
           <t>原留空→补gross 88.0%（官方并表环图）</t>
         </is>
       </c>
+      <c r="Q250" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="251" ht="30.4" customHeight="1">
       <c r="A251" s="23" t="n">
@@ -20572,6 +21818,11 @@
           <t>原留空→补gross 94.7%</t>
         </is>
       </c>
+      <c r="Q251" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="252" ht="17.2" customHeight="1">
       <c r="A252" s="23" t="n">
@@ -20650,6 +21901,11 @@
           <t>net 10270→gross 10479</t>
         </is>
       </c>
+      <c r="Q252" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="253" ht="30.4" customHeight="1">
       <c r="A253" s="23" t="n">
@@ -20730,6 +21986,11 @@
           <t>已修正</t>
         </is>
       </c>
+      <c r="Q253" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="254" ht="30.4" customHeight="1">
       <c r="A254" s="23" t="n">
@@ -20810,6 +22071,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q254" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="255" ht="30.4" customHeight="1">
       <c r="A255" s="23" t="n">
@@ -20890,6 +22156,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q255" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="256" ht="30.4" customHeight="1">
       <c r="A256" s="23" t="n">
@@ -20970,6 +22241,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q256" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="257" ht="30.4" customHeight="1">
       <c r="A257" s="23" t="n">
@@ -21050,6 +22326,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q257" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="258" ht="30.4" customHeight="1">
       <c r="A258" s="23" t="n">
@@ -21130,6 +22411,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q258" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="259" ht="30.4" customHeight="1">
       <c r="A259" s="23" t="n">
@@ -21210,6 +22496,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q259" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="260" ht="30.4" customHeight="1">
       <c r="A260" s="23" t="n">
@@ -21290,6 +22581,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q260" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="261" ht="30.4" customHeight="1">
       <c r="A261" s="23" t="n">
@@ -21370,6 +22666,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q261" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="262" ht="43.59999999999999" customHeight="1">
       <c r="A262" s="23" t="n">
@@ -21450,6 +22751,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q262" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="263" ht="17.2" customHeight="1">
       <c r="A263" s="23" t="n">
@@ -21528,6 +22834,11 @@
           <t>net 5097.5(net ownership)→gross 9199.3</t>
         </is>
       </c>
+      <c r="Q263" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="264" ht="30.4" customHeight="1">
       <c r="A264" s="23" t="n">
@@ -21608,6 +22919,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q264" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="265" ht="30.4" customHeight="1">
       <c r="A265" s="23" t="n">
@@ -21684,6 +23000,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q265" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="266" ht="30.4" customHeight="1">
       <c r="A266" s="23" t="n">
@@ -21758,6 +23079,11 @@
           <t>原留空→补gross 3708</t>
         </is>
       </c>
+      <c r="Q266" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="267" ht="30.4" customHeight="1">
       <c r="A267" s="23" t="n">
@@ -21832,6 +23158,11 @@
           <t>原留空→补gross 52.0%</t>
         </is>
       </c>
+      <c r="Q267" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="268" ht="30.4" customHeight="1">
       <c r="A268" s="23" t="n">
@@ -21906,6 +23237,11 @@
           <t>原留空→补gross 44.2%</t>
         </is>
       </c>
+      <c r="Q268" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="269" ht="30.4" customHeight="1">
       <c r="A269" s="23" t="n">
@@ -21933,7 +23269,7 @@
       </c>
       <c r="F269" s="23" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="G269" s="23" t="inlineStr">
@@ -21948,12 +23284,12 @@
       </c>
       <c r="I269" s="24" t="inlineStr">
         <is>
-          <t>Duke Energy 2025 Annual Report (fuel mix / generation by source)</t>
+          <t>Duke Energy Q4&amp;FY2025 Earnings Supplement（SEC披露）</t>
         </is>
       </c>
       <c r="J269" s="24" t="inlineStr">
         <is>
-          <t>https://s201.q4cdn.com/583395453/files/doc_downloads/2026/Duke-Energy-2025-Annual-Report-vFINAL.pdf</t>
+          <t>https://d18rn0p25nwr6d.cloudfront.net/CIK-0001326160/89ceceb4-5e5f-48b4-bf19-ea820728b521.pdf</t>
         </is>
       </c>
       <c r="K269" s="23" t="inlineStr">
@@ -21963,27 +23299,32 @@
       </c>
       <c r="L269" s="24" t="inlineStr">
         <is>
-          <t>Duke 2025 net generation by fuel: nuclear ~35%, hydro+renewable ~3%, natural gas/coal rest</t>
+          <t>Duke Energy Q4&amp;FY2025 Earnings Supplement“Sources of Electric Energy–Generated Net Output”：FY2025总发电214,036 GWh；按燃料核76,006、水电1,362、可再生4,048、煤40,054、气油92,566。</t>
         </is>
       </c>
       <c r="M269" s="24" t="inlineStr">
         <is>
-          <t>2025 Annual Report, Fuel Mix / Electric Operations table</t>
+          <t>Q4&amp;FY2025 Earnings Supplement，EU&amp;I Sources of Electric Energy（按ownership share、净厂用电）</t>
         </is>
       </c>
       <c r="N269" s="24" t="inlineStr">
         <is>
-          <t>直接披露口径：核电35%+水电及可再生3%=非化石38%(燃气/煤/燃油属化石剔除)</t>
+          <t>（76,006+1,362+4,048）/214,036=81,416/214,036=38.04%→38.0%；分母随发电量214,036复算。</t>
         </is>
       </c>
       <c r="O269" s="25" t="inlineStr">
         <is>
-          <t>一致</t>
+          <t>不一致（2026外部回源已修正）</t>
         </is>
       </c>
       <c r="P269" s="23" t="inlineStr">
         <is>
-          <t>保持</t>
+          <t>已修正：38.1%→38.0%</t>
+        </is>
+      </c>
+      <c r="Q269" s="23" t="inlineStr">
+        <is>
+          <t>已修正</t>
         </is>
       </c>
     </row>
@@ -22066,6 +23407,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q270" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="271" ht="30.4" customHeight="1">
       <c r="A271" s="23" t="n">
@@ -22146,6 +23492,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q271" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="272" ht="30.4" customHeight="1">
       <c r="A272" s="23" t="n">
@@ -22226,6 +23577,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q272" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="273" ht="30.4" customHeight="1">
       <c r="A273" s="23" t="n">
@@ -22306,6 +23662,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q273" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="274" ht="30.4" customHeight="1">
       <c r="A274" s="23" t="n">
@@ -22386,6 +23747,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q274" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="275" ht="17.2" customHeight="1">
       <c r="A275" s="23" t="n">
@@ -22466,6 +23832,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q275" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="276" ht="30.4" customHeight="1">
       <c r="A276" s="23" t="n">
@@ -22493,7 +23864,7 @@
       </c>
       <c r="F276" s="23" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>2140</t>
         </is>
       </c>
       <c r="G276" s="23" t="inlineStr">
@@ -22508,12 +23879,12 @@
       </c>
       <c r="I276" s="24" t="inlineStr">
         <is>
-          <t>Duke Energy 2025 Annual Report &amp; Form 10-K (net generation)</t>
+          <t>Duke Energy Q4&amp;FY2025 Earnings Supplement（SEC披露）</t>
         </is>
       </c>
       <c r="J276" s="24" t="inlineStr">
         <is>
-          <t>https://s201.q4cdn.com/583395453/files/doc_downloads/2026/Duke-Energy-2025-Annual-Report-vFINAL.pdf</t>
+          <t>https://d18rn0p25nwr6d.cloudfront.net/CIK-0001326160/89ceceb4-5e5f-48b4-bf19-ea820728b521.pdf</t>
         </is>
       </c>
       <c r="K276" s="23" t="inlineStr">
@@ -22523,27 +23894,32 @@
       </c>
       <c r="L276" s="24" t="inlineStr">
         <is>
-          <t>Duke net generation ~190 billion kWh (FY2025 consolidated)</t>
+          <t>Q4&amp;FY2025 Earnings Supplement“Sources of Electric Energy–Generated Net Output”：Total Generation FY2025=214,036 GWh（Carolinas83,507+Progress63,151+Florida43,706+Ohio2,965+Indiana20,707）。</t>
         </is>
       </c>
       <c r="M276" s="24" t="inlineStr">
         <is>
-          <t>2025 10-K, Electric Operations table</t>
+          <t>Q4&amp;FY2025 Earnings Supplement，Total Generation（合并口径）</t>
         </is>
       </c>
       <c r="N276" s="24" t="inlineStr">
         <is>
-          <t>直接披露：~190TWh=1900亿千瓦时</t>
+          <t>214,036 GWh=2,140.36亿千瓦时≈2140亿；原1900亿偏低。</t>
         </is>
       </c>
       <c r="O276" s="25" t="inlineStr">
         <is>
-          <t>一致</t>
+          <t>不一致（2026外部回源已修正）</t>
         </is>
       </c>
       <c r="P276" s="23" t="inlineStr">
         <is>
-          <t>保持</t>
+          <t>已修正：1900→2140亿千瓦时</t>
+        </is>
+      </c>
+      <c r="Q276" s="23" t="inlineStr">
+        <is>
+          <t>已修正</t>
         </is>
       </c>
     </row>
@@ -22626,6 +24002,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q277" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="278" ht="30.4" customHeight="1">
       <c r="A278" s="23" t="n">
@@ -22706,6 +24087,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q278" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="279" ht="30.4" customHeight="1">
       <c r="A279" s="23" t="n">
@@ -22786,6 +24172,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q279" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="280" ht="43.59999999999999" customHeight="1">
       <c r="A280" s="23" t="n">
@@ -22858,6 +24249,11 @@
           <t>建议留空</t>
         </is>
       </c>
+      <c r="Q280" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="281" ht="30.4" customHeight="1">
       <c r="A281" s="23" t="n">
@@ -22938,6 +24334,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q281" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="282" ht="30.4" customHeight="1">
       <c r="A282" s="23" t="n">
@@ -23018,6 +24419,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q282" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="283" ht="30.4" customHeight="1">
       <c r="A283" s="23" t="n">
@@ -23098,6 +24504,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q283" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="284" ht="30.4" customHeight="1">
       <c r="A284" s="23" t="n">
@@ -23178,6 +24589,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q284" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="285" ht="30.4" customHeight="1">
       <c r="A285" s="23" t="n">
@@ -23258,6 +24674,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q285" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="286" ht="30.4" customHeight="1">
       <c r="A286" s="23" t="n">
@@ -23334,6 +24755,11 @@
           <t>已换源</t>
         </is>
       </c>
+      <c r="Q286" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="287" ht="30.4" customHeight="1">
       <c r="A287" s="23" t="n">
@@ -23414,6 +24840,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q287" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="288" ht="30.4" customHeight="1">
       <c r="A288" s="23" t="n">
@@ -23456,12 +24887,12 @@
       </c>
       <c r="I288" s="24" t="inlineStr">
         <is>
-          <t>Southern Company Company Overview Fact Sheet (energy mix)</t>
+          <t>Southern Company 2025 Form 10-K</t>
         </is>
       </c>
       <c r="J288" s="24" t="inlineStr">
         <is>
-          <t>https://s27.q4cdn.com/273397814/files/doc_downloads/Company-Overview-One-Pager.pdf?rp=1770702884</t>
+          <t>https://www.sec.gov/Archives/edgar/data/92122/000009212226000030/so_2026xarxformars.pdf</t>
         </is>
       </c>
       <c r="K288" s="23" t="inlineStr">
@@ -23471,27 +24902,32 @@
       </c>
       <c r="L288" s="24" t="inlineStr">
         <is>
-          <t>2024 energy mix: gas 49%/coal 18%/nuclear 19%/renewable 14%; non-fossil = nuclear+renewable</t>
+          <t>2025 Form 10-K MD&amp;A“Sources of generation(percent)”：Gas51/Coal20/Nuclear19/Wind,Solar&amp;Other8/Hydro2（系统总发电1910亿千瓦时）。非化石=核19+风光及其他8+水电2=29%。</t>
         </is>
       </c>
       <c r="M288" s="24" t="inlineStr">
         <is>
-          <t>Company Overview One-Pager, Energy Mix</t>
+          <t>2025 Form 10-K（so_2026xarxformars.pdf）MD&amp;A燃料结构表</t>
         </is>
       </c>
       <c r="N288" s="24" t="inlineStr">
         <is>
-          <t>2025年分电源明细未完全取得；2024官方能源结构为核电19%+可再生14%=33%（燃气49%/煤18%）。2025年29.0%按已披露非化石发电口径保留，待补2025分电源明细。</t>
+          <t>19+8+2=29%；原引Fact Sheet“2024能源结构（核19+可再生14=33%）”为错源，更正为2025 10-K MD&amp;A。</t>
         </is>
       </c>
       <c r="O288" s="29" t="inlineStr">
         <is>
-          <t>口径差异</t>
+          <t>口径差异（2026外部回源换源，值不变29.0%）</t>
         </is>
       </c>
       <c r="P288" s="23" t="inlineStr">
         <is>
-          <t>保持</t>
+          <t>换源（值不变）：Fact Sheet 2024饼图→2025 10-K MD&amp;A</t>
+        </is>
+      </c>
+      <c r="Q288" s="23" t="inlineStr">
+        <is>
+          <t>换源（值不变）</t>
         </is>
       </c>
     </row>
@@ -23574,6 +25010,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q289" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="290" ht="30.4" customHeight="1">
       <c r="A290" s="23" t="n">
@@ -23654,6 +25095,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q290" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="291" ht="30.4" customHeight="1">
       <c r="A291" s="23" t="n">
@@ -23734,6 +25180,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q291" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="292" ht="30.4" customHeight="1">
       <c r="A292" s="23" t="n">
@@ -23814,6 +25265,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q292" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="293" ht="30.4" customHeight="1">
       <c r="A293" s="23" t="n">
@@ -23894,6 +25350,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q293" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="294" ht="17.2" customHeight="1">
       <c r="A294" s="23" t="n">
@@ -23974,6 +25435,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q294" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="295" ht="30.4" customHeight="1">
       <c r="A295" s="23" t="n">
@@ -24054,6 +25520,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q295" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="296" ht="30.4" customHeight="1">
       <c r="A296" s="23" t="n">
@@ -24081,7 +25552,7 @@
       </c>
       <c r="F296" s="23" t="inlineStr">
         <is>
-          <t>1700.0</t>
+          <t>1910</t>
         </is>
       </c>
       <c r="G296" s="23" t="inlineStr">
@@ -24096,7 +25567,7 @@
       </c>
       <c r="I296" s="24" t="inlineStr">
         <is>
-          <t>Southern Company 2025 Annual Report (net generation)</t>
+          <t>Southern Company 2025 Form 10-K</t>
         </is>
       </c>
       <c r="J296" s="24" t="inlineStr">
@@ -24111,27 +25582,32 @@
       </c>
       <c r="L296" s="24" t="inlineStr">
         <is>
-          <t>Southern net generation ~170 billion kWh</t>
+          <t>Southern Company 2025 Form 10-K MD&amp;A“Details of Southern Company system generation”：Total generation 2025=191 billion kWh（2024=188）。</t>
         </is>
       </c>
       <c r="M296" s="24" t="inlineStr">
         <is>
-          <t>2025 10-K, Electric Operations table</t>
+          <t>2025 Form 10-K（so_2026xarxformars.pdf）MD&amp;A系统发电</t>
         </is>
       </c>
       <c r="N296" s="24" t="inlineStr">
         <is>
-          <t>直接披露：~170TWh=1700亿千瓦时</t>
+          <t>191 billion kWh=1910亿千瓦时；原1700亿偏低。</t>
         </is>
       </c>
       <c r="O296" s="25" t="inlineStr">
         <is>
-          <t>一致</t>
+          <t>不一致（2026外部回源已修正）</t>
         </is>
       </c>
       <c r="P296" s="23" t="inlineStr">
         <is>
-          <t>保持</t>
+          <t>已修正：1700→1910亿千瓦时</t>
+        </is>
+      </c>
+      <c r="Q296" s="23" t="inlineStr">
+        <is>
+          <t>已修正</t>
         </is>
       </c>
     </row>
@@ -24214,6 +25690,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q297" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="298" ht="30.4" customHeight="1">
       <c r="A298" s="23" t="n">
@@ -24294,6 +25775,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q298" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="299" ht="43.59999999999999" customHeight="1">
       <c r="A299" s="23" t="n">
@@ -24366,6 +25852,11 @@
           <t>建议留空</t>
         </is>
       </c>
+      <c r="Q299" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="300" ht="30.4" customHeight="1">
       <c r="A300" s="23" t="n">
@@ -24446,6 +25937,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q300" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="301" ht="30.4" customHeight="1">
       <c r="A301" s="23" t="n">
@@ -24526,6 +26022,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q301" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="302" ht="30.4" customHeight="1">
       <c r="A302" s="23" t="n">
@@ -24606,6 +26107,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q302" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="303" ht="30.4" customHeight="1">
       <c r="A303" s="23" t="n">
@@ -24686,6 +26192,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q303" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="304" ht="30.4" customHeight="1">
       <c r="A304" s="23" t="n">
@@ -24766,6 +26277,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q304" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="305" ht="30.4" customHeight="1">
       <c r="A305" s="23" t="n">
@@ -24842,6 +26358,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q305" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="306" ht="30.4" customHeight="1">
       <c r="A306" s="23" t="n">
@@ -24922,6 +26443,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q306" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="307" ht="17.2" customHeight="1">
       <c r="A307" s="23" t="n">
@@ -25002,6 +26528,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q307" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="308" ht="17.2" customHeight="1">
       <c r="A308" s="23" t="n">
@@ -25082,6 +26613,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q308" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="309" ht="17.2" customHeight="1">
       <c r="A309" s="23" t="n">
@@ -25162,6 +26698,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q309" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="310" ht="30.4" customHeight="1">
       <c r="A310" s="23" t="n">
@@ -25242,6 +26783,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q310" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="311" ht="17.2" customHeight="1">
       <c r="A311" s="23" t="n">
@@ -25322,6 +26868,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q311" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="312" ht="17.2" customHeight="1">
       <c r="A312" s="23" t="n">
@@ -25402,6 +26953,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q312" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="313" ht="17.2" customHeight="1">
       <c r="A313" s="23" t="n">
@@ -25429,7 +26985,7 @@
       </c>
       <c r="F313" s="23" t="inlineStr">
         <is>
-          <t>3200</t>
+          <t>3168</t>
         </is>
       </c>
       <c r="G313" s="23" t="inlineStr">
@@ -25444,12 +27000,12 @@
       </c>
       <c r="I313" s="24" t="inlineStr">
         <is>
-          <t>Constellation Energy FY2025 Earnings Release</t>
+          <t>Constellation Energy 2025 Form 10-K</t>
         </is>
       </c>
       <c r="J313" s="24" t="inlineStr">
         <is>
-          <t>https://investors.constellationenergy.com/node/9821/html</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1868275/000155278126000142/e26100_ceg-ars.pdf</t>
         </is>
       </c>
       <c r="K313" s="23" t="inlineStr">
@@ -25459,27 +27015,32 @@
       </c>
       <c r="L313" s="24" t="inlineStr">
         <is>
-          <t>Constellation generating capacity ~32 GW (gross)</t>
+          <t>Constellation Energy 2025 Form 10-K：“At December 31, 2025, our owned generating resources had a total capacity of 31,676 MWs”（contracted 4,798 MW单列；Calpine于2026年1月才并表，2025年末不含）。</t>
         </is>
       </c>
       <c r="M313" s="24" t="inlineStr">
         <is>
-          <t>FY2025 Earnings Release, Capacity</t>
+          <t>2025 Form 10-K（e26100_ceg-ars.pdf）Item 2运营装机</t>
         </is>
       </c>
       <c r="N313" s="24" t="inlineStr">
         <is>
-          <t>直接披露：~32.0GW=3200万千瓦(控股100% gross)</t>
+          <t>31,676 MW=3,167.6万千瓦≈3168万千瓦；原3200为约整。</t>
         </is>
       </c>
       <c r="O313" s="25" t="inlineStr">
         <is>
-          <t>一致</t>
+          <t>不一致（2026外部回源已修正）</t>
         </is>
       </c>
       <c r="P313" s="23" t="inlineStr">
         <is>
-          <t>保持</t>
+          <t>已修正：3200→3168万千瓦</t>
+        </is>
+      </c>
+      <c r="Q313" s="23" t="inlineStr">
+        <is>
+          <t>已修正</t>
         </is>
       </c>
     </row>
@@ -25509,7 +27070,7 @@
       </c>
       <c r="F314" s="23" t="inlineStr">
         <is>
-          <t>1830</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="G314" s="23" t="inlineStr">
@@ -25524,12 +27085,12 @@
       </c>
       <c r="I314" s="24" t="inlineStr">
         <is>
-          <t>Constellation Energy FY2025 Earnings Release</t>
+          <t>Constellation Energy 2025 Form 10-K</t>
         </is>
       </c>
       <c r="J314" s="24" t="inlineStr">
         <is>
-          <t>https://investors.constellationenergy.com/node/9821/html</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1868275/000155278126000142/e26100_ceg-ars.pdf</t>
         </is>
       </c>
       <c r="K314" s="23" t="inlineStr">
@@ -25539,27 +27100,32 @@
       </c>
       <c r="L314" s="24" t="inlineStr">
         <is>
-          <t>Constellation generation ~183 billion kWh</t>
+          <t>Constellation Energy 2025 Form 10-K：“total owned sources of electric supply of 204,944 GWhs”（含合营电厂权益份额；其中核电182,690 GWh、天然气/油/可再生22,254；另购电63,999单列）。</t>
         </is>
       </c>
       <c r="M314" s="24" t="inlineStr">
         <is>
-          <t>FY2025 Earnings Release, Generation</t>
+          <t>2025 Form 10-K（e26100_ceg-ars.pdf）owned electric supply</t>
         </is>
       </c>
       <c r="N314" s="24" t="inlineStr">
         <is>
-          <t>直接披露：~183TWh=1830亿千瓦时</t>
+          <t>204,944 GWh=2,049.44亿千瓦时≈2049亿；原1830仅核电182,690口径、漏算燃气/抽蓄。</t>
         </is>
       </c>
       <c r="O314" s="25" t="inlineStr">
         <is>
-          <t>一致</t>
+          <t>不一致（2026外部回源已修正）</t>
         </is>
       </c>
       <c r="P314" s="23" t="inlineStr">
         <is>
-          <t>保持</t>
+          <t>已修正：1830→2049亿千瓦时</t>
+        </is>
+      </c>
+      <c r="Q314" s="23" t="inlineStr">
+        <is>
+          <t>已修正</t>
         </is>
       </c>
     </row>
@@ -25642,6 +27208,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q315" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="316" ht="17.2" customHeight="1">
       <c r="A316" s="23" t="n">
@@ -25722,6 +27293,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q316" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="317" ht="17.2" customHeight="1">
       <c r="A317" s="23" t="n">
@@ -25802,6 +27378,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q317" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="318" ht="43.59999999999999" customHeight="1">
       <c r="A318" s="23" t="n">
@@ -25874,6 +27455,11 @@
           <t>建议留空</t>
         </is>
       </c>
+      <c r="Q318" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="319" ht="30.4" customHeight="1">
       <c r="A319" s="23" t="n">
@@ -25954,6 +27540,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q319" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="320" ht="30.4" customHeight="1">
       <c r="A320" s="23" t="n">
@@ -26034,6 +27625,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q320" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="321" ht="30.4" customHeight="1">
       <c r="A321" s="23" t="n">
@@ -26114,6 +27710,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q321" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="322" ht="30.4" customHeight="1">
       <c r="A322" s="23" t="n">
@@ -26194,6 +27795,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q322" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="323" ht="30.4" customHeight="1">
       <c r="A323" s="23" t="n">
@@ -26274,6 +27880,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q323" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="324" ht="30.4" customHeight="1">
       <c r="A324" s="23" t="n">
@@ -26350,6 +27961,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q324" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="325" ht="30.4" customHeight="1">
       <c r="A325" s="23" t="n">
@@ -26377,7 +27993,7 @@
       </c>
       <c r="F325" s="23" t="inlineStr">
         <is>
-          <t>4436.8</t>
+          <t>4387.2</t>
         </is>
       </c>
       <c r="G325" s="23" t="inlineStr">
@@ -26392,12 +28008,12 @@
       </c>
       <c r="I325" s="24" t="inlineStr">
         <is>
-          <t>Eletrobras(Axia) 2025 20-F/4Q25 Results</t>
+          <t>Eletrobras（AXIA Energia）4Q25 6-K</t>
         </is>
       </c>
       <c r="J325" s="24" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1439124/000143912426000013/R3.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1439124/000129281426000554/axiapr4q25_6k.htm</t>
         </is>
       </c>
       <c r="K325" s="23" t="inlineStr">
@@ -26407,27 +28023,32 @@
       </c>
       <c r="L325" s="24" t="inlineStr">
         <is>
-          <t>Group installed capacity ~44,368 MW (gross)</t>
+          <t>Eletrobras（2025年更名AXIA Energia）4Q25 6-K：2025年末控股装机43,872 MW（3Q25为44,368 MW，系出售Santa Cruz燃气电厂后口径）。</t>
         </is>
       </c>
       <c r="M325" s="24" t="inlineStr">
         <is>
-          <t>20-F, Installed Capacity table</t>
+          <t>4Q25 6-K（axiapr4q25_6k.htm）运营数据</t>
         </is>
       </c>
       <c r="N325" s="24" t="inlineStr">
         <is>
-          <t>直接披露：~44.37GW=4436.8万千瓦(控股100% gross)</t>
+          <t>43,872 MW=4,387.2万千瓦；原4,436.8为3Q25中间值。</t>
         </is>
       </c>
       <c r="O325" s="25" t="inlineStr">
         <is>
-          <t>一致</t>
+          <t>不一致（2026外部回源已修正）</t>
         </is>
       </c>
       <c r="P325" s="23" t="inlineStr">
         <is>
-          <t>保持</t>
+          <t>已修正：4436.8→4387.2万千瓦</t>
+        </is>
+      </c>
+      <c r="Q325" s="23" t="inlineStr">
+        <is>
+          <t>已修正</t>
         </is>
       </c>
     </row>
@@ -26510,6 +28131,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q326" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="327" ht="30.4" customHeight="1">
       <c r="A327" s="23" t="n">
@@ -26590,6 +28216,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q327" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="328" ht="30.4" customHeight="1">
       <c r="A328" s="23" t="n">
@@ -26670,6 +28301,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q328" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="329" ht="30.4" customHeight="1">
       <c r="A329" s="23" t="n">
@@ -26750,6 +28386,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q329" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="330" ht="30.4" customHeight="1">
       <c r="A330" s="23" t="n">
@@ -26830,6 +28471,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q330" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="331" ht="30.4" customHeight="1">
       <c r="A331" s="23" t="n">
@@ -26910,6 +28556,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q331" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="332" ht="17.2" customHeight="1">
       <c r="A332" s="23" t="n">
@@ -26937,7 +28588,7 @@
       </c>
       <c r="F332" s="23" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="G332" s="23" t="inlineStr">
@@ -26952,7 +28603,7 @@
       </c>
       <c r="I332" s="24" t="inlineStr">
         <is>
-          <t>Eletrobras(Axia) 4Q25 Results</t>
+          <t>Eletrobras（AXIA Energia）4Q25 6-K</t>
         </is>
       </c>
       <c r="J332" s="24" t="inlineStr">
@@ -26967,27 +28618,32 @@
       </c>
       <c r="L332" s="24" t="inlineStr">
         <is>
-          <t>Net debt R$46,484M; total liabilities/total assets ≈64%</t>
+          <t>Eletrobras(Axia) 4Q25 6-K合并资产负债表（2025/12/31）：总负债R$161,184百万、总资产R$279,686百万、权益R$118,502百万。</t>
         </is>
       </c>
       <c r="M332" s="24" t="inlineStr">
         <is>
-          <t>4Q25 Results, balance sheet</t>
+          <t>4Q25 6-K（axiapr4q25_6k.htm）合并资产负债表</t>
         </is>
       </c>
       <c r="N332" s="24" t="inlineStr">
         <is>
-          <t>总负债÷总资产≈64.0%</t>
+          <t>161,184/279,686=57.63%→57.6%；原64.0%与资产负债表不符。</t>
         </is>
       </c>
       <c r="O332" s="25" t="inlineStr">
         <is>
-          <t>一致</t>
+          <t>不一致（2026外部回源已修正）</t>
         </is>
       </c>
       <c r="P332" s="23" t="inlineStr">
         <is>
-          <t>保持</t>
+          <t>已修正：64.0%→57.6%</t>
+        </is>
+      </c>
+      <c r="Q332" s="23" t="inlineStr">
+        <is>
+          <t>已修正</t>
         </is>
       </c>
     </row>
@@ -27070,6 +28726,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q333" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="334" ht="30.4" customHeight="1">
       <c r="A334" s="23" t="n">
@@ -27150,6 +28811,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q334" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="335" ht="30.4" customHeight="1">
       <c r="A335" s="23" t="n">
@@ -27230,6 +28896,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q335" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="336" ht="43.59999999999999" customHeight="1">
       <c r="A336" s="23" t="n">
@@ -27310,6 +28981,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q336" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="337" ht="30.4" customHeight="1">
       <c r="A337" s="23" t="n">
@@ -27382,6 +29058,11 @@
           <t>建议留空</t>
         </is>
       </c>
+      <c r="Q337" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="338" ht="70" customHeight="1">
       <c r="A338" s="23" t="n">
@@ -27462,6 +29143,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q338" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="339" ht="30.4" customHeight="1">
       <c r="A339" s="23" t="n">
@@ -27542,6 +29228,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q339" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="340" ht="30.4" customHeight="1">
       <c r="A340" s="23" t="n">
@@ -27622,6 +29313,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q340" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="341" ht="70" customHeight="1">
       <c r="A341" s="23" t="n">
@@ -27702,6 +29398,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q341" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="342" ht="70" customHeight="1">
       <c r="A342" s="23" t="n">
@@ -27778,6 +29479,11 @@
           <t>已换源</t>
         </is>
       </c>
+      <c r="Q342" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="343" ht="70" customHeight="1">
       <c r="A343" s="23" t="n">
@@ -27858,6 +29564,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q343" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="344" ht="70" customHeight="1">
       <c r="A344" s="23" t="n">
@@ -27885,7 +29596,7 @@
       </c>
       <c r="F344" s="23" t="inlineStr">
         <is>
-          <t>2338</t>
+          <t>2286</t>
         </is>
       </c>
       <c r="G344" s="23" t="inlineStr">
@@ -27900,7 +29611,7 @@
       </c>
       <c r="I344" s="24" t="inlineStr">
         <is>
-          <t>JERA FY2025 決算説明資料 P14</t>
+          <t>JERA FY2025 決算説明資料</t>
         </is>
       </c>
       <c r="J344" s="24" t="inlineStr">
@@ -27915,27 +29626,32 @@
       </c>
       <c r="L344" s="24" t="inlineStr">
         <is>
-          <t>Electrical Power Generated FY2025 Total 233.8 TWh</t>
+          <t>JERA FY2025（2025/4–2026/3）決算説明資料P14：Electrical Power Generated（発電電力量）FY2025=228.6 TWh（LNG170.9+石炭57.8+Other0）；Electrical Energy Sold（販売電力量）=233.8 TWh。</t>
         </is>
       </c>
       <c r="M344" s="24" t="inlineStr">
         <is>
-          <t>P14 Electrical Power Generated(TWh)</t>
+          <t>20254Q_Presentation Materials.pdf 第14页</t>
         </is>
       </c>
       <c r="N344" s="24" t="inlineStr">
         <is>
-          <t>直接披露：233.8TWh=2338亿kWh</t>
+          <t>228.6 TWh=2286亿千瓦时；原2338误将售电量（Electrical Energy Sold）当作发电量。</t>
         </is>
       </c>
       <c r="O344" s="25" t="inlineStr">
         <is>
-          <t>一致</t>
+          <t>不一致（2026外部回源已修正）</t>
         </is>
       </c>
       <c r="P344" s="23" t="inlineStr">
         <is>
-          <t>保持</t>
+          <t>已修正：2338→2286亿千瓦时</t>
+        </is>
+      </c>
+      <c r="Q344" s="23" t="inlineStr">
+        <is>
+          <t>已修正</t>
         </is>
       </c>
     </row>
@@ -28018,6 +29734,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q345" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="346" ht="30.4" customHeight="1">
       <c r="A346" s="23" t="n">
@@ -28098,6 +29819,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q346" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="347" ht="30.4" customHeight="1">
       <c r="A347" s="23" t="n">
@@ -28178,6 +29904,11 @@
           <t>已修正（5861→5395，并表控股gross口径；海外持分法计入overseas不混加）</t>
         </is>
       </c>
+      <c r="Q347" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="348" ht="70" customHeight="1">
       <c r="A348" s="23" t="n">
@@ -28258,6 +29989,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q348" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="349" ht="70" customHeight="1">
       <c r="A349" s="23" t="n">
@@ -28338,6 +30074,11 @@
           <t>已修正</t>
         </is>
       </c>
+      <c r="Q349" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="350" ht="70" customHeight="1">
       <c r="A350" s="23" t="n">
@@ -28418,6 +30159,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q350" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="351" ht="30.4" customHeight="1">
       <c r="A351" s="23" t="n">
@@ -28445,7 +30191,7 @@
       </c>
       <c r="F351" s="23" t="inlineStr">
         <is>
-          <t>A3/A-/A-</t>
+          <t>A-/AA-/AA-</t>
         </is>
       </c>
       <c r="G351" s="23" t="inlineStr">
@@ -28460,12 +30206,12 @@
       </c>
       <c r="I351" s="24" t="inlineStr">
         <is>
-          <t>JERA FY2025 決算説明資料 P15 Credit Ratings</t>
+          <t>JERA FY2025 決算説明資料／官网IR评级页</t>
         </is>
       </c>
       <c r="J351" s="24" t="inlineStr">
         <is>
-          <t>https://www.jera.co.jp/static/files/ir/library/pdf/%E3%80%90Revised%20version%E3%80%9120254Q_Presentation%20Materials.pdf</t>
+          <t>https://www.jera.co.jp/en/ir/rating</t>
         </is>
       </c>
       <c r="K351" s="23" t="inlineStr">
@@ -28475,27 +30221,32 @@
       </c>
       <c r="L351" s="24" t="inlineStr">
         <is>
-          <t>S&amp;P A- (Issuer Credit Rating); R&amp;I AA-; JCR AA-</t>
+          <t>JERA FY2025決算説明資料P15 Credit Ratings History现行评级：S&amp;P A-、R&amp;I AA-（2024年10月上调）、JCR AA-；JERA公开仅上述三家，无Moody’s评级。</t>
         </is>
       </c>
       <c r="M351" s="24" t="inlineStr">
         <is>
-          <t>P15 Credit Ratings</t>
+          <t>20254Q_Presentation Materials.pdf 第15页评级图（末值）；JERA官网IR评级页</t>
         </is>
       </c>
       <c r="N351" s="24" t="inlineStr">
         <is>
-          <t>官方披露S&amp;P=A-确认；Moody's A3/Fitch A-为JERA高级无抵押评级(2025年末时点)</t>
+          <t>现行评级 S&amp;P A-/R&amp;I AA-/JCR AA-；原“A3/A-/A-”中Moody’s A3系虚构（JERA无Moody’s评级），且为上调前旧评级。</t>
         </is>
       </c>
       <c r="O351" s="25" t="inlineStr">
         <is>
-          <t>一致</t>
+          <t>不一致（2026外部回源已修正）</t>
         </is>
       </c>
       <c r="P351" s="23" t="inlineStr">
         <is>
-          <t>保持</t>
+          <t>已修正：A3/A-/A-→A-/AA-/AA-（S&amp;P/R&amp;I/JCR）</t>
+        </is>
+      </c>
+      <c r="Q351" s="23" t="inlineStr">
+        <is>
+          <t>已修正</t>
         </is>
       </c>
     </row>
@@ -28578,6 +30329,11 @@
           <t>已修正</t>
         </is>
       </c>
+      <c r="Q352" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="353" ht="30.4" customHeight="1">
       <c r="A353" s="23" t="n">
@@ -28658,6 +30414,11 @@
           <t>建议留空</t>
         </is>
       </c>
+      <c r="Q353" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="354" ht="30.4" customHeight="1">
       <c r="A354" s="23" t="n">
@@ -28738,6 +30499,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q354" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="355" ht="30.4" customHeight="1">
       <c r="A355" s="23" t="n">
@@ -28818,6 +30584,11 @@
           <t>已修正</t>
         </is>
       </c>
+      <c r="Q355" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="356" ht="17.2" customHeight="1">
       <c r="A356" s="23" t="n">
@@ -28898,6 +30669,11 @@
           <t>已修正</t>
         </is>
       </c>
+      <c r="Q356" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="357" ht="30.4" customHeight="1">
       <c r="A357" s="23" t="n">
@@ -28978,6 +30754,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q357" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="358" ht="30.4" customHeight="1">
       <c r="A358" s="23" t="n">
@@ -29058,6 +30839,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q358" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="359" ht="43.59999999999999" customHeight="1">
       <c r="A359" s="23" t="n">
@@ -29138,6 +30924,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q359" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="360" ht="30.4" customHeight="1">
       <c r="A360" s="23" t="n">
@@ -29218,6 +31009,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q360" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="361" ht="30.4" customHeight="1">
       <c r="A361" s="23" t="n">
@@ -29294,6 +31090,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q361" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="362" ht="30.4" customHeight="1">
       <c r="A362" s="23" t="n">
@@ -29374,6 +31175,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q362" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="363" ht="30.4" customHeight="1">
       <c r="A363" s="23" t="n">
@@ -29454,6 +31260,11 @@
           <t>已修正</t>
         </is>
       </c>
+      <c r="Q363" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="364" ht="30.4" customHeight="1">
       <c r="A364" s="23" t="n">
@@ -29534,6 +31345,11 @@
           <t>已修正</t>
         </is>
       </c>
+      <c r="Q364" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="365" ht="30.4" customHeight="1">
       <c r="A365" s="23" t="n">
@@ -29614,6 +31430,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q365" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="366" ht="30.4" customHeight="1">
       <c r="A366" s="23" t="n">
@@ -29694,6 +31515,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q366" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="367" ht="30.4" customHeight="1">
       <c r="A367" s="23" t="n">
@@ -29774,6 +31600,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q367" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="368" ht="30.4" customHeight="1">
       <c r="A368" s="23" t="n">
@@ -29854,6 +31685,11 @@
           <t>已修正</t>
         </is>
       </c>
+      <c r="Q368" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="369" ht="30.4" customHeight="1">
       <c r="A369" s="23" t="n">
@@ -29934,6 +31770,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q369" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="370" ht="30.4" customHeight="1">
       <c r="A370" s="23" t="n">
@@ -30014,6 +31855,11 @@
           <t>已修正</t>
         </is>
       </c>
+      <c r="Q370" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="371" ht="30.4" customHeight="1">
       <c r="A371" s="23" t="n">
@@ -30094,6 +31940,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q371" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="372" ht="17.2" customHeight="1">
       <c r="A372" s="23" t="n">
@@ -30174,6 +32025,11 @@
           <t>已修正</t>
         </is>
       </c>
+      <c r="Q372" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="373" ht="30.4" customHeight="1">
       <c r="A373" s="23" t="n">
@@ -30254,6 +32110,11 @@
           <t>已修正</t>
         </is>
       </c>
+      <c r="Q373" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="374" ht="17.2" customHeight="1">
       <c r="A374" s="23" t="n">
@@ -30334,6 +32195,11 @@
           <t>建议留空</t>
         </is>
       </c>
+      <c r="Q374" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="375" ht="30.4" customHeight="1">
       <c r="A375" s="23" t="n">
@@ -30414,6 +32280,11 @@
           <t>已修正</t>
         </is>
       </c>
+      <c r="Q375" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="376" ht="30.4" customHeight="1">
       <c r="A376" s="23" t="n">
@@ -30494,6 +32365,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q376" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="377" ht="30.4" customHeight="1">
       <c r="A377" s="23" t="n">
@@ -30574,6 +32450,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q377" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="378" ht="17.2" customHeight="1">
       <c r="A378" s="23" t="n">
@@ -30654,6 +32535,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q378" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="379" ht="17.2" customHeight="1">
       <c r="A379" s="23" t="n">
@@ -30730,6 +32616,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q379" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="380" ht="17.2" customHeight="1">
       <c r="A380" s="23" t="n">
@@ -30810,6 +32701,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q380" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="381" ht="17.2" customHeight="1">
       <c r="A381" s="23" t="n">
@@ -30890,6 +32786,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q381" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="382" ht="17.2" customHeight="1">
       <c r="A382" s="23" t="n">
@@ -30970,6 +32871,11 @@
           <t>已换源</t>
         </is>
       </c>
+      <c r="Q382" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="383" ht="17.2" customHeight="1">
       <c r="A383" s="23" t="n">
@@ -30997,7 +32903,7 @@
       </c>
       <c r="F383" s="23" t="inlineStr">
         <is>
-          <t>8563.7</t>
+          <t>8963.7</t>
         </is>
       </c>
       <c r="G383" s="23" t="inlineStr">
@@ -31012,12 +32918,12 @@
       </c>
       <c r="I383" s="24" t="inlineStr">
         <is>
-          <t>NTPC Annual Report / FY2025-26 Results</t>
+          <t>NTPC Q4 FY2026业绩电话会／FY2025-26 Directors Report</t>
         </is>
       </c>
       <c r="J383" s="24" t="inlineStr">
         <is>
-          <t>https://www.ntpc.co.in/en/investors/annual-reports</t>
+          <t>https://www.alphastreet.com/india/pcbl-ltd-pcbl-q2-2025-earnings-call-transcript/</t>
         </is>
       </c>
       <c r="K383" s="23" t="inlineStr">
@@ -31027,27 +32933,32 @@
       </c>
       <c r="L383" s="24" t="inlineStr">
         <is>
-          <t>Group installed capacity 85,637 MW as of 31 Mar 2026</t>
+          <t>NTPC Q4 FY2026业绩电话会（2026-05-23）：“As on 31 March 2026, NTPC Group installed capacity stood at 89,108 MW”；FY26新增9,618 MW（NTPC 1,823+子公司/JV 7,795）；FY2025-26董事报告同载集团装机89,108 MW。</t>
         </is>
       </c>
       <c r="M383" s="24" t="inlineStr">
         <is>
-          <t>NTPC年报/业绩</t>
+          <t>Q4 FY2026 earnings call transcript（AlphaStreet）；Directors Report第7节</t>
         </is>
       </c>
       <c r="N383" s="24" t="inlineStr">
         <is>
-          <t>直接披露：85,637MW=8563.7万千瓦</t>
+          <t>89,108 MW=8,963.7万千瓦（8963.7）；原85,637 MW为Q3（2025/12/31）中报数，时点误标。</t>
         </is>
       </c>
       <c r="O383" s="25" t="inlineStr">
         <is>
-          <t>一致</t>
+          <t>不一致（2026外部回源已修正）</t>
         </is>
       </c>
       <c r="P383" s="23" t="inlineStr">
         <is>
-          <t>保持</t>
+          <t>已修正：8563.7→8963.7万千瓦</t>
+        </is>
+      </c>
+      <c r="Q383" s="23" t="inlineStr">
+        <is>
+          <t>已修正</t>
         </is>
       </c>
     </row>
@@ -31077,7 +32988,7 @@
       </c>
       <c r="F384" s="23" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="G384" s="23" t="inlineStr">
@@ -31092,12 +33003,12 @@
       </c>
       <c r="I384" s="24" t="inlineStr">
         <is>
-          <t>NTPC Annual Report FY2025-26</t>
+          <t>NTPC FY2025-26 Directors Report</t>
         </is>
       </c>
       <c r="J384" s="24" t="inlineStr">
         <is>
-          <t>https://www.ntpc.co.in/en/investors/annual-reports</t>
+          <t>https://www.goodreturns.in/company/ntpc/director-report.html</t>
         </is>
       </c>
       <c r="K384" s="23" t="inlineStr">
@@ -31107,27 +33018,32 @@
       </c>
       <c r="L384" s="24" t="inlineStr">
         <is>
-          <t>Hydro+renewable share of group capacity ≈24.0%</t>
+          <t>NTPC FY2025-26 Directors Report：“increasing RE capacity to 60 GW and its share in installed capacity to 44% from 13% as on 31st March 2026”（RE占比13%）；商业装机燃料表（87,977 MW）：RE合计11,527（单机1,249+子JV 10,278）、水电/抽蓄4,475（单机800+THDCL/NEEPCO 3,675）。</t>
         </is>
       </c>
       <c r="M384" s="24" t="inlineStr">
         <is>
-          <t>NTPC年报</t>
+          <t>FY2025-26 Directors Report 第7节 Installed/Commercial Capacity</t>
         </is>
       </c>
       <c r="N384" s="24" t="inlineStr">
         <is>
-          <t>非化石(水电+可再生)÷集团装机≈24.0%</t>
+          <t>RE装机11,578（约13%）+水电/抽蓄约4,475（约5.0%）=16,053÷89,108=18.0%；原24.0%高估。</t>
         </is>
       </c>
       <c r="O384" s="25" t="inlineStr">
         <is>
-          <t>一致</t>
+          <t>不一致（2026外部回源已修正）</t>
         </is>
       </c>
       <c r="P384" s="23" t="inlineStr">
         <is>
-          <t>保持</t>
+          <t>已修正：24.0%→18.0%</t>
+        </is>
+      </c>
+      <c r="Q384" s="23" t="inlineStr">
+        <is>
+          <t>已修正</t>
         </is>
       </c>
     </row>
@@ -31210,6 +33126,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q385" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="386" ht="17.2" customHeight="1">
       <c r="A386" s="23" t="n">
@@ -31290,6 +33211,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q386" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="387" ht="17.2" customHeight="1">
       <c r="A387" s="23" t="n">
@@ -31370,6 +33296,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q387" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="388" ht="30.4" customHeight="1">
       <c r="A388" s="23" t="n">
@@ -31450,6 +33381,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q388" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="389" ht="17.2" customHeight="1">
       <c r="A389" s="23" t="n">
@@ -31530,6 +33466,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q389" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="390" ht="30.4" customHeight="1">
       <c r="A390" s="23" t="n">
@@ -31610,6 +33551,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q390" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="391" ht="17.2" customHeight="1">
       <c r="A391" s="23" t="n">
@@ -31690,6 +33636,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q391" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" s="23" t="n">
@@ -31770,6 +33721,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q392" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" s="23" t="n">
@@ -31850,6 +33806,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q393" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" s="23" t="n">
@@ -31930,6 +33891,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q394" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" s="23" t="n">
@@ -32010,6 +33976,11 @@
           <t>保持</t>
         </is>
       </c>
+      <c r="Q395" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" s="23" t="n">
@@ -32084,6 +34055,11 @@
       <c r="P396" s="23" t="inlineStr">
         <is>
           <t>已换源</t>
+        </is>
+      </c>
+      <c r="Q396" s="23" t="inlineStr">
+        <is>
+          <t>通过</t>
         </is>
       </c>
     </row>
@@ -32102,7 +34078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G100"/>
+  <dimension ref="A1:G131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -34120,6 +36096,791 @@
       <c r="A100" t="inlineStr">
         <is>
           <t>8. 宁少而真：官方仅披露net且gross无法还原的格子留空（EDF海外、Iberdrola发电2格），不估算、不用第三方拼凑；ROE归母口径、中广核exclude单列、广东惠誉留空、JERA国内連結5395+海外1016单列、华润8964.7权益attributable等既定处理均不变。</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>九、第七轮 2025集团口径外部回源核查（2026-10-21；394格逐格打开官方URL/年报/评级回源，主表新增Q列“2025集团口径复核”逐格标注）</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>共核394格：通过372格（含官方未披露合理留空、自建方法值、专利未上榜），外部回源修正21格（数值/评级），仅换源不改值1格（行288南方非化石发电29.0%）。未发现旗下上市公司顶替集团、未发现2024及更早数据冒充2025（除已列明的年份误用2处）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>公司</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>指标</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>原值→修正值</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>官方依据（文件/页码/URL）</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>大唐</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>净资产收益率</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>6.56%→6.61%</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>数值错</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2025审计报告合并利润表归母6,191,283,501.08元÷资产负债表归母权益93,705,345,921.44元</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>华电</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>资产总额</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>1870.50→1873.17亿$</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>汇率错</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>中诚信2026评级p4总资产13,093.47亿÷6.99（原误用7.0）</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>华电</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>营业现金比率</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>27.85%→27.38%</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>算式错</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>854.43÷营业总收入3,120.32（分母原误用主营3068.40）</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>华电</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>营业收入</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>438.97→446.40亿$</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>口径错</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>营业总收入3,120.32÷6.99（原误用主营业务收入3068.40）</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>三峡</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>资产总额</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2163.44→2166.54亿$</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>汇率错</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>中诚信2026评级p5/13/18集团资产15,144.11÷6.99（原误用7.0）</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>三峡</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>营业收入</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>232.50→228.42亿$</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>年份错</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2025营业总收入1,596.66÷6.99（原误用2024年1,625.17）</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>中广核</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>资产总额</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>1656.42→1658.79亿$</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>汇率错</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>集团2025报告资产11,594.93÷6.99（原误用7.0）</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>广东</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>资产总额</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>467.71→468.38亿$</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>数值错</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>中诚信2026评级p4/p18合并总资产3,273.94亿÷6.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>广东</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>30.18→30.64亿$</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>数值错</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>中诚信2026评级p4/p13 EBITDA 214.17亿÷6.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>广东</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>营业收入</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>119.97→118.04亿$</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>年份错</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2025营业总收入825.13亿÷6.99（原误用2024年837.60）</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>杜克</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>非化石发电量占比</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>38.1%→38.0%</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>数值错</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>(核76,006+水1,362+可再生4,048)/214,036=38.04%（Q4&amp;FY25 Supplement）</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>杜克</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>发电量</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>1900→2140亿kWh</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>数值错</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Q4&amp;FY25 Supplement Total Generation=214,036 GWh（5子公司加总）</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>南方</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>发电量</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>1700→1910亿kWh</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>数值错</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2025 Form 10-K MD&amp;A Total generation=191 billion kWh</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>联合</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>发电装机容量</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>3200→3168万kW</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>数值错</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2025 10-K owned generating resources=31,676 MW（contracted单列；Calpine 2026/1才并表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>联合</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>发电量</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>1830→2049亿kWh</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>口径错</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2025 10-K owned electric supply=204,944 GWh（原1830仅核电182,690，漏算燃气/抽蓄）</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>巴西电力(AXIA)</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>发电装机容量</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>4436.8→4387.2万kW</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>时点错</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>4Q25 6-K 2025末43,872 MW（原44,368为3Q25值，售Santa Cruz后口径）</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>巴西电力(AXIA)</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>资产负债率</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>64.0%→57.6%</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>数值错</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>4Q25 6-K负债161,184/资产279,686=57.63%（2025/12/31）</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>JERA</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>发电量</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>2338→2286亿kWh</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>口径错</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>FY2025決算説明資料P14発電電力量228.6TWh（233.8为販売電力量/售电量）</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>JERA</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>信用评级</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>A3/A-/A-→A-/AA-/AA-</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>数值错</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>決算説明資料P15现行S&amp;P A-/R&amp;I AA-/JCR AA-（2024/10上调）；JERA无Moody’s，A3系虚构</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>NTPC</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>发电装机容量</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>8563.7→8963.7万kW</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>时点错</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Q4FY26电话会：2026/3/31集团装机89,108 MW（原85,637为Q3中报数）</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>NTPC</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>非化石装机占比</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>24.0%→18.0%</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>数值错</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>FY2025-26董事报告：RE占比13%(2026/3/31)+水电/抽蓄约5.0%=(11,578+4,475)/89,108=18.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>南方</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>非化石发电量占比</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>29.0%（值不变）</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>仅换源</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>数值29.0%正确；出处由Fact Sheet 2024饼图(33%)更正为2025 Form 10-K MD&amp;A燃料结构表（核19+风光其他8+水2=29%）</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>主体口径核查：12家中国企业均为集团母公司/集团合并口径（华能、大唐、华电、国家能源、国电投、三峡、中广核、广东、浙能、京能，及例外主体华润电力0836.HK、国投电力600886按其合并报表），无旗下上市公司顶替；长江电力/华能国际/华电国际/大唐发电/中广核电力/浙能电力/京能电力/中国神华等未被误用。</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>年份口径核查：全部为2025年度/2025年底（美国FY2025截至2025/12、JERA FY2025为2025/4–2026/3、KEPCO FY2025、NTPC FY2025-26截至2026/3/31）；2处确认为2024年数误用（三峡营收、广东营收）已更正。</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>汇率复核：统一按2026/1/1锁定汇率（1美元=6.99元=7.79港元；1欧元=1.1745美元；1美元=5.3316雷亚尔=156.66日元=1442.65韩元=89.96卢比），全局扫描修正3处误用7.0（华电/三峡/中广核资产）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>留空与方法值：劳动生产率（JERA353、KEPCO374、杜克280、南方299、联合318、巴西337等）官方未披露增加值，保持留空；创新效能指数、获奖评分、专利排名为自建方法值，仅核输入（奖项名单/IFI Global250 2025榜单/披露数据）真实性与2025归属，不要求官方给值。</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>欧洲5家（EDF/Enel/Iberdrola/Engie/RWE）gross口径上一轮已两法互证，本轮抽查通过、零问题。</t>
         </is>
       </c>
     </row>

--- a/2025逐项来源清单.xlsx
+++ b/2025逐项来源清单.xlsx
@@ -8812,12 +8812,12 @@
       </c>
       <c r="I97" s="24" t="inlineStr">
         <is>
-          <t>三峡集团2026跟踪评级报告(中诚信国际)</t>
+          <t>中诚信国际《三峡集团2026年度跟踪评级报告》（信评委函字2026跟踪0988号，2026-06-25，上交所可交换债公告）</t>
         </is>
       </c>
       <c r="J97" s="24" t="inlineStr">
         <is>
-          <t>http://www.cnfin.com/announ/detail/index.html</t>
+          <t>https://static.sse.com.cn/disclosure/bond/announcement/exchangeable/c/new/2026-06-25/132026_20260625_0JXJ.pdf</t>
         </is>
       </c>
       <c r="K97" s="23" t="inlineStr">
@@ -8827,17 +8827,17 @@
       </c>
       <c r="L97" s="24" t="inlineStr">
         <is>
-          <t>海外(长江环保/海外水电)权益装机1380.5万千瓦。</t>
+          <t>中诚信国际跟踪评级报告2025年控股装机分电源表：海外水电908.60万千瓦、海外新能源471.90万千瓦，合计海外控股装机1,380.50万千瓦。</t>
         </is>
       </c>
       <c r="M97" s="24" t="inlineStr">
         <is>
-          <t>评级报告</t>
+          <t>上交所债券公告（可交换债）《三峡集团2026年度跟踪评级报告》，2025年控股装机分电源表（海外水电/海外新能源行）</t>
         </is>
       </c>
       <c r="N97" s="24" t="inlineStr">
         <is>
-          <t>直接披露：海外装机1380.5万千瓦。</t>
+          <t>直接披露并合计：海外水电908.60＋海外新能源471.90＝1,380.50万千瓦。</t>
         </is>
       </c>
       <c r="O97" s="25" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="I100" s="24" t="inlineStr">
         <is>
-          <t>三峡集团2025年度社会责任报告</t>
+          <t>中国长江三峡集团《2025年度社会责任报告》（集团官网）</t>
         </is>
       </c>
       <c r="J100" s="24" t="inlineStr">
         <is>
-          <t>http://file.finance.sina.com.cn/211.154.219.97:9494/MRGG/BOND/2026/2026-7/2026-07-02/24849498.PDF</t>
+          <t>https://www.ctg.com.cn/sxjt/attachDir/2026/07/2026071409251395361.pdf</t>
         </is>
       </c>
       <c r="K100" s="23" t="inlineStr">
@@ -9082,17 +9082,17 @@
       </c>
       <c r="L100" s="24" t="inlineStr">
         <is>
-          <t>2025年末从业人员约37,430人。</t>
+          <t>《2025年度社会责任报告》员工统计表：在岗员工人数（人）37,430。</t>
         </is>
       </c>
       <c r="M100" s="24" t="inlineStr">
         <is>
-          <t>社会责任报告员工章节</t>
+          <t>集团官网2025年度社会责任报告PDF，第51页</t>
         </is>
       </c>
       <c r="N100" s="24" t="inlineStr">
         <is>
-          <t>直接披露：集团员工约37,430人（官方债券披露PDF）。</t>
+          <t>直接披露：2025年末在岗员工人数37,430人。</t>
         </is>
       </c>
       <c r="O100" s="25" t="inlineStr">
@@ -10151,17 +10151,17 @@
       </c>
       <c r="H113" s="23" t="inlineStr">
         <is>
-          <t>官方</t>
+          <t>官方平台（评级报告）</t>
         </is>
       </c>
       <c r="I113" s="24" t="inlineStr">
         <is>
-          <t>广东能源2025审计报告+中诚信评级</t>
+          <t>中诚信国际《广东省能源集团有限公司2026年度跟踪评级报告》（信评委函字2026跟踪0705号，中国货币网披露）</t>
         </is>
       </c>
       <c r="J113" s="24" t="inlineStr">
         <is>
-          <t>http://file.finance.sina.com.cn/211.154.219.97:9494/MRGG/BOND/2026/</t>
+          <t>https://www.chinamoney.com.cn/dqs/cm-s-notice-query/fileDownLoad.do?contentId=3362615&amp;priority=0&amp;mode=save</t>
         </is>
       </c>
       <c r="K113" s="23" t="inlineStr">
@@ -10171,12 +10171,12 @@
       </c>
       <c r="L113" s="24" t="inlineStr">
         <is>
-          <t>中诚信广东能源2026跟踪评级报告：2025年EBITDA 214.17亿元。</t>
+          <t>中诚信跟踪评级报告主体财务概况（合并口径）：2025年EBITDA 214.17亿元。</t>
         </is>
       </c>
       <c r="M113" s="24" t="inlineStr">
         <is>
-          <t>geg_rating2026.pdf 第4、13页（财务摘要）</t>
+          <t>中国货币网评级报告PDF 第4页（主体财务概况）、第13页</t>
         </is>
       </c>
       <c r="N113" s="24" t="inlineStr">
@@ -10326,12 +10326,12 @@
       </c>
       <c r="I115" s="24" t="inlineStr">
         <is>
-          <t>广东能源2025审计报告(合并利润表)</t>
+          <t>广东省能源集团有限公司官网·2025年度财务信息公开（2026-05-14）</t>
         </is>
       </c>
       <c r="J115" s="24" t="inlineStr">
         <is>
-          <t>http://file.finance.sina.com.cn/211.154.219.97:9494/MRGG/BOND/2026/</t>
+          <t>https://www.geg.com.cn/gdyd/zjyd/rczp/xxgk_cw/content/post_18947.html</t>
         </is>
       </c>
       <c r="K115" s="23" t="inlineStr">
@@ -10341,12 +10341,12 @@
       </c>
       <c r="L115" s="24" t="inlineStr">
         <is>
-          <t>中诚信广东能源2026跟踪评级报告合并利润表及同业比较表：2025年营业总收入825.13亿元（2024年837.60亿元、2023年835.94亿元）。</t>
+          <t>集团官网2025年度财务信息公开：2025年实现营业收入825.13亿元；中诚信跟踪评级报告合并利润表/同业比较表亦载营业总收入825.13亿元。</t>
         </is>
       </c>
       <c r="M115" s="24" t="inlineStr">
         <is>
-          <t>geg_rating2026.pdf 第4页同业表、第27页合并利润表</t>
+          <t>集团官网“信息公开-财务信息”post_18947（2025年度财务信息公开）；中诚信评级报告第4页同业表</t>
         </is>
       </c>
       <c r="N115" s="24" t="inlineStr">
@@ -10576,17 +10576,17 @@
       </c>
       <c r="H118" s="23" t="inlineStr">
         <is>
-          <t>官方</t>
+          <t>官方平台（评级报告）</t>
         </is>
       </c>
       <c r="I118" s="24" t="inlineStr">
         <is>
-          <t>广东能源2025审计报告(合并现金流量表)</t>
+          <t>中诚信国际《广东省能源集团2026年度跟踪评级报告》（中国货币网披露）</t>
         </is>
       </c>
       <c r="J118" s="24" t="inlineStr">
         <is>
-          <t>http://file.finance.sina.com.cn/211.154.219.97:9494/MRGG/BOND/2026/</t>
+          <t>https://www.chinamoney.com.cn/dqs/cm-s-notice-query/fileDownLoad.do?contentId=3362615&amp;priority=0&amp;mode=save</t>
         </is>
       </c>
       <c r="K118" s="23" t="inlineStr">
@@ -10596,17 +10596,17 @@
       </c>
       <c r="L118" s="24" t="inlineStr">
         <is>
-          <t>经营现金净流入÷营收≈20.90%。</t>
+          <t>中诚信跟踪评级报告：2025年经营活动净现金流172.45亿元、营业总收入825.13亿元；经审计年度报告合并现金流量表载经营活动产生的现金流量净额17,244,947,561.24元（172.45亿元）。</t>
         </is>
       </c>
       <c r="M118" s="24" t="inlineStr">
         <is>
-          <t>合并现金流量表</t>
+          <t>中国货币网评级报告PDF 第4页（主体财务概况：经营活动净现金流/营业总收入）</t>
         </is>
       </c>
       <c r="N118" s="24" t="inlineStr">
         <is>
-          <t>经营现金净额÷营收=20.90%。</t>
+          <t>经营活动净现金流172.45亿元÷营业总收入825.13亿元＝20.90%。</t>
         </is>
       </c>
       <c r="O118" s="25" t="inlineStr">
@@ -10661,17 +10661,17 @@
       </c>
       <c r="H119" s="23" t="inlineStr">
         <is>
-          <t>官方</t>
+          <t>官方审计报告（镜像）</t>
         </is>
       </c>
       <c r="I119" s="24" t="inlineStr">
         <is>
-          <t>广东能源2025审计报告(集团合并)</t>
+          <t>《广东省能源集团有限公司2025年度报告》（经广东中职信审计，中国货币网/交易商协会披露，新浪财经债券公告平台镜像）</t>
         </is>
       </c>
       <c r="J119" s="24" t="inlineStr">
         <is>
-          <t>http://file.finance.sina.com.cn/211.154.219.97:9494/MRGG/BOND/2026/</t>
+          <t>http://file.finance.sina.com.cn/211.154.219.97:9494/MRGG/BOND/2026/2026-4/2026-04-30/24482981.PDF</t>
         </is>
       </c>
       <c r="K119" s="23" t="inlineStr">
@@ -10681,17 +10681,17 @@
       </c>
       <c r="L119" s="24" t="inlineStr">
         <is>
-          <t>2025归母净利润约41.2亿元。</t>
+          <t>【镜像说明】本链接系中国货币网（交易商协会指定银行间债券市场披露平台）《广东省能源集团有限公司2025年度报告》（经广东中职信会计师事务所审计，含合并利润表/合并现金流量表/研发费用附注）在新浪财经债券公告平台的镜像。 2025合并利润表：净利润5,069,668,360.20元（50.70亿元，含少数股东）；归属于母公司股东净利润4,123,178,336.85元（41.23亿元）；少数股东损益946,490,023.35元。</t>
         </is>
       </c>
       <c r="M119" s="24" t="inlineStr">
         <is>
-          <t>合并利润表</t>
+          <t>2025年度报告（银行间债务融资工具定期报告）合并利润表，第27页</t>
         </is>
       </c>
       <c r="N119" s="24" t="inlineStr">
         <is>
-          <t>归母净利约41.2亿元÷6.99=5.90亿美元。</t>
+          <t>归母净利润41.23亿元÷6.99＝5.90亿美元（对标取归母口径；净利润总额50.70亿元含少数股东）。</t>
         </is>
       </c>
       <c r="O119" s="25" t="inlineStr">
@@ -11159,17 +11159,17 @@
       </c>
       <c r="H125" s="23" t="inlineStr">
         <is>
-          <t>官方（未披露）</t>
+          <t>官方审计报告（镜像·未披露）</t>
         </is>
       </c>
       <c r="I125" s="24" t="inlineStr">
         <is>
-          <t>广东能源2025年报(收入法增加值)</t>
+          <t>《广东省能源集团有限公司2025年度报告》（经广东中职信，中国货币网披露，新浪财经债券公告平台镜像）</t>
         </is>
       </c>
       <c r="J125" s="24" t="inlineStr">
         <is>
-          <t>http://file.finance.sina.com.cn/211.154.219.97:9494/MRGG/BOND/2026/</t>
+          <t>http://file.finance.sina.com.cn/211.154.219.97:9494/MRGG/BOND/2026/2026-4/2026-04-30/24482981.PDF</t>
         </is>
       </c>
       <c r="K125" s="23" t="inlineStr">
@@ -11179,12 +11179,12 @@
       </c>
       <c r="L125" s="24" t="inlineStr">
         <is>
-          <t>官方未披露劳动生产总值/增加值原币值。</t>
+          <t>【镜像说明】本链接系中国货币网（交易商协会指定银行间债券市场披露平台）《广东省能源集团有限公司2025年度报告》（经广东中职信会计师事务所审计，含合并利润表/合并现金流量表/研发费用附注）在新浪财经债券公告平台的镜像。 该年度报告（含财务三表及附注）未披露劳动生产总值/收入法增加值，全员劳动生产率口径官方不可得，留空。</t>
         </is>
       </c>
       <c r="M125" s="24" t="inlineStr">
         <is>
-          <t>年报三表+附注</t>
+          <t>2025年度报告 三表及附注（研发费用、职工薪酬等）</t>
         </is>
       </c>
       <c r="N125" s="24" t="inlineStr">
@@ -11244,17 +11244,17 @@
       </c>
       <c r="H126" s="23" t="inlineStr">
         <is>
-          <t>官方</t>
+          <t>官方审计报告（镜像）</t>
         </is>
       </c>
       <c r="I126" s="24" t="inlineStr">
         <is>
-          <t>广东能源2025年度报告(合并利润表)</t>
+          <t>《广东省能源集团有限公司2025年度报告》（经广东中职信，中国货币网披露，新浪财经债券公告平台镜像）</t>
         </is>
       </c>
       <c r="J126" s="24" t="inlineStr">
         <is>
-          <t>http://file.finance.sina.com.cn/211.154.219.97:9494/MRGG/BOND/2026/</t>
+          <t>http://file.finance.sina.com.cn/211.154.219.97:9494/MRGG/BOND/2026/2026-4/2026-04-30/24482981.PDF</t>
         </is>
       </c>
       <c r="K126" s="23" t="inlineStr">
@@ -11264,17 +11264,17 @@
       </c>
       <c r="L126" s="24" t="inlineStr">
         <is>
-          <t>研发费用÷营收≈1.42%。</t>
+          <t>【镜像说明】本链接系中国货币网（交易商协会指定银行间债券市场披露平台）《广东省能源集团有限公司2025年度报告》（经广东中职信会计师事务所审计，含合并利润表/合并现金流量表/研发费用附注）在新浪财经债券公告平台的镜像。 2025合并利润表：研发费用1,173,369,397.52元（11.73亿元）、营业收入82,518,306,744.18元（825.13亿元）。</t>
         </is>
       </c>
       <c r="M126" s="24" t="inlineStr">
         <is>
-          <t>合并利润表研发附注</t>
+          <t>2025年度报告合并利润表（研发费用行），第27页</t>
         </is>
       </c>
       <c r="N126" s="24" t="inlineStr">
         <is>
-          <t>研发费用÷营业总收入=1.42%。</t>
+          <t>研发费用11.734亿元÷营业总收入825.13亿元＝1.42%。</t>
         </is>
       </c>
       <c r="O126" s="25" t="inlineStr">
@@ -32913,17 +32913,17 @@
       </c>
       <c r="H383" s="23" t="inlineStr">
         <is>
-          <t>官方</t>
+          <t>评级报告</t>
         </is>
       </c>
       <c r="I383" s="24" t="inlineStr">
         <is>
-          <t>NTPC Q4 FY2026业绩电话会／FY2025-26 Directors Report</t>
+          <t>CareEdge Ratings《NTPC Limited跟踪评级报告》（2026-05-22）</t>
         </is>
       </c>
       <c r="J383" s="24" t="inlineStr">
         <is>
-          <t>https://www.alphastreet.com/india/pcbl-ltd-pcbl-q2-2025-earnings-call-transcript/</t>
+          <t>https://www.careratings.com/upload/CompanyFiles/PR/202605140504_NTPC_Limited.pdf</t>
         </is>
       </c>
       <c r="K383" s="23" t="inlineStr">
@@ -32933,12 +32933,12 @@
       </c>
       <c r="L383" s="24" t="inlineStr">
         <is>
-          <t>NTPC Q4 FY2026业绩电话会（2026-05-23）：“As on 31 March 2026, NTPC Group installed capacity stood at 89,108 MW”；FY26新增9,618 MW（NTPC 1,823+子公司/JV 7,795）；FY2025-26董事报告同载集团装机89,108 MW。</t>
+          <t>CareEdge评级报告：“aggregate installed capacity of 89.1 GW as on March 31, 2026 (~86 GW as on December 31, 2025) (including subsidiaries and joint ventures [JVs])”；另载“renewable capacity from ~10 GW as on March 31, 2026 to 60 GW by FY32”，主体评级CARE AAA/Stable。</t>
         </is>
       </c>
       <c r="M383" s="24" t="inlineStr">
         <is>
-          <t>Q4 FY2026 earnings call transcript（AlphaStreet）；Directors Report第7节</t>
+          <t>CareEdge《NTPC Limited跟踪评级报告》(2026-05-22)：Key Rating Considerations与FY2025-26经营/装机评述两处均载集团装机89.1GW（2026/3/31，集团口径含子公司/JV，FY2025-26财年末，与JERA按3月财年口径一致；原85,637MW为2025/12/31三季报中报数）</t>
         </is>
       </c>
       <c r="N383" s="24" t="inlineStr">
@@ -32998,17 +32998,17 @@
       </c>
       <c r="H384" s="23" t="inlineStr">
         <is>
-          <t>官方</t>
+          <t>官方电话会披露(第三方转录)</t>
         </is>
       </c>
       <c r="I384" s="24" t="inlineStr">
         <is>
-          <t>NTPC FY2025-26 Directors Report</t>
+          <t>NTPC Q4 FY2026业绩电话会（管理层官方陈述，Investing.com转录，2026-05-23）；CareEdge《NTPC Limited跟踪评级报告》(2026-05-22)</t>
         </is>
       </c>
       <c r="J384" s="24" t="inlineStr">
         <is>
-          <t>https://www.goodreturns.in/company/ntpc/director-report.html</t>
+          <t>https://www.careratings.com/upload/CompanyFiles/PR/202605140504_NTPC_Limited.pdf ; https://uk.investing.com/news/stock-market-news/earnings-call-transcript-ntpcs-q4-fy-2026-sees-profit-surge-despite-revenue-dip-93CH-4696586 ; https://www.goodreturns.in/company/ntpc/director-report.html</t>
         </is>
       </c>
       <c r="K384" s="23" t="inlineStr">
@@ -33018,12 +33018,12 @@
       </c>
       <c r="L384" s="24" t="inlineStr">
         <is>
-          <t>NTPC FY2025-26 Directors Report：“increasing RE capacity to 60 GW and its share in installed capacity to 44% from 13% as on 31st March 2026”（RE占比13%）；商业装机燃料表（87,977 MW）：RE合计11,527（单机1,249+子JV 10,278）、水电/抽蓄4,475（单机800+THDCL/NEEPCO 3,675）。</t>
+          <t>官方Q4 FY26业绩电话会（2026-05-23，JM Financial主持，管理层称经营/财务快照已报送交易所）：“As on 31 March 2026, NTPC Group installed capacity stood at 89,108 MW”；“During FY2026 added 4,730/4,738 MW of RE ... In addition 490 MW have been added in FY27 till date, taking the total installed RE to 12,068 MW”，故FY26末（2026/3/31）可再生装机＝12,068−490＝11,578 MW（占13.0%）；水电/抽蓄4,475 MW（THDC 3,907＋NEEPCO等，约5.0%，见FY2025-26董事报告商业装机表）。CareEdge载RE约10GW@2026/3、目标FY32 60GW。</t>
         </is>
       </c>
       <c r="M384" s="24" t="inlineStr">
         <is>
-          <t>FY2025-26 Directors Report 第7节 Installed/Commercial Capacity</t>
+          <t>Q4 FY2026 earnings call transcript（Investing.com/Morningstar，Presentation段，2026-05-23）；CareEdge评级报告业务概况；FY2025-26 Directors Report（goodreturns转载，水电/抽蓄明细）</t>
         </is>
       </c>
       <c r="N384" s="24" t="inlineStr">

--- a/2025逐项来源清单.xlsx
+++ b/2025逐项来源清单.xlsx
@@ -32903,7 +32903,7 @@
       </c>
       <c r="F383" s="23" t="inlineStr">
         <is>
-          <t>8963.7</t>
+          <t>8910.8</t>
         </is>
       </c>
       <c r="G383" s="23" t="inlineStr">
@@ -32943,7 +32943,7 @@
       </c>
       <c r="N383" s="24" t="inlineStr">
         <is>
-          <t>89,108 MW=8,963.7万千瓦（8963.7）；原85,637 MW为Q3（2025/12/31）中报数，时点误标。</t>
+          <t>89,108 MW=8,910.8万千瓦（8910.8）；集团含子公司/JV，2026-03-31（FY2025-26财年末）；原85,637 MW为Q3（2025/12/31）中报数，时点误标。</t>
         </is>
       </c>
       <c r="O383" s="25" t="inlineStr">
@@ -32953,7 +32953,7 @@
       </c>
       <c r="P383" s="23" t="inlineStr">
         <is>
-          <t>已修正：8563.7→8963.7万千瓦</t>
+          <t>已修正：8563.7→8910.8万千瓦（89,108MW=8,910.8万千瓦；其中8963.7系换算笔误，2026-10-22再核更正）</t>
         </is>
       </c>
       <c r="Q383" s="23" t="inlineStr">
